--- a/artfynd/A 62861-2025 artfynd.xlsx
+++ b/artfynd/A 62861-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1248,6 +1248,6805 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>130800713</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79219</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Skinnaråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>489149</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6720123</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>130800726</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79219</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Skinnaråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>489323</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6720025</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>130800706</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79219</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Skinnaråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>489143</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6720009</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>130800693</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79219</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Skinnaråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>489211</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6720001</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>130800627</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57859</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Skinnaråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>489163</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6719987</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>130800672</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79219</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Skinnaråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>489170</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6720188</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>130800622</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57859</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Skinnaråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>489171</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6720048</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>130800721</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79219</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Skinnaråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>489189</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6720073</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>130800641</v>
+      </c>
+      <c r="B15" t="n">
+        <v>8451</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Skinnaråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>489210</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6720036</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>130800671</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79219</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Skinnaråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>489159</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6720170</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>130800634</v>
+      </c>
+      <c r="B17" t="n">
+        <v>8451</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Skinnaråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>489196</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6720103</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>130800689</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79219</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Skinnaråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>489171</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6720037</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>130800609</v>
+      </c>
+      <c r="B19" t="n">
+        <v>91774</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Skinnaråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>489172</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6720186</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>130800621</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57859</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Skinnaråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>489175</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6720065</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>130800710</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79219</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Skinnaråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>489124</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6720109</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>130800668</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79219</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Skinnaråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>489197</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6720167</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>130800690</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79219</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Skinnaråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>489198</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6720010</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>130800718</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79219</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Skinnaråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>489189</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6720114</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>130800682</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79219</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Skinnaråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>489151</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6720086</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>130800695</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79219</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Skinnaråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>489231</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6719941</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>130800687</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79219</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Skinnaråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>489175</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6720053</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>130800725</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79219</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Skinnaråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>489332</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6720052</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>130800606</v>
+      </c>
+      <c r="B29" t="n">
+        <v>92145</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>2062</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Ulltickeporing</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Skeletocutis brevispora</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Skinnaråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>489169</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6720185</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>130800696</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79219</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Skinnaråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>489243</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6719933</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>130800688</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79219</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Skinnaråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>489168</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6720046</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>130800678</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79219</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Skinnaråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>489131</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6720117</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>130800716</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79219</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Skinnaråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>489172</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6720145</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>130800669</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79219</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Skinnaråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>489170</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6720167</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>130800712</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79219</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Skinnaråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>489143</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6720114</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>130800679</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79219</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Skinnaråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>489122</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6720120</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>130800676</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79219</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Skinnaråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>489151</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6720144</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>130800666</v>
+      </c>
+      <c r="B38" t="n">
+        <v>79219</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Skinnaråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>489208</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6720174</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>130800608</v>
+      </c>
+      <c r="B39" t="n">
+        <v>92145</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>2062</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Ulltickeporing</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Skeletocutis brevispora</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Skinnaråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>489214</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6719996</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>130800714</v>
+      </c>
+      <c r="B40" t="n">
+        <v>79219</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Skinnaråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>489163</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6720122</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>130800707</v>
+      </c>
+      <c r="B41" t="n">
+        <v>79219</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Skinnaråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>489119</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6720040</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>130800677</v>
+      </c>
+      <c r="B42" t="n">
+        <v>79219</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Skinnaråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>489132</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6720123</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>130800681</v>
+      </c>
+      <c r="B43" t="n">
+        <v>79219</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Skinnaråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>489138</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6720092</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>130800684</v>
+      </c>
+      <c r="B44" t="n">
+        <v>79219</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Skinnaråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>489177</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6720066</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>130800709</v>
+      </c>
+      <c r="B45" t="n">
+        <v>79219</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Skinnaråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>489094</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6720086</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>130800667</v>
+      </c>
+      <c r="B46" t="n">
+        <v>79219</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Skinnaråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>489199</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6720176</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>130800722</v>
+      </c>
+      <c r="B47" t="n">
+        <v>79219</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Skinnaråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>489207</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6720040</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>130800610</v>
+      </c>
+      <c r="B48" t="n">
+        <v>91774</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Skinnaråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>489216</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6719995</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>130800704</v>
+      </c>
+      <c r="B49" t="n">
+        <v>79219</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Skinnaråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>489180</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6719972</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>130800715</v>
+      </c>
+      <c r="B50" t="n">
+        <v>79219</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Skinnaråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>489166</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6720127</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>130800630</v>
+      </c>
+      <c r="B51" t="n">
+        <v>57859</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Skinnaråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>489207</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6720041</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>130800673</v>
+      </c>
+      <c r="B52" t="n">
+        <v>79219</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Skinnaråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>489180</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6720180</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>130800675</v>
+      </c>
+      <c r="B53" t="n">
+        <v>79219</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Skinnaråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>489147</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6720156</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>10:12</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>10:12</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>130800680</v>
+      </c>
+      <c r="B54" t="n">
+        <v>79219</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Skinnaråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>489131</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6720110</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>130800637</v>
+      </c>
+      <c r="B55" t="n">
+        <v>8451</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Skinnaråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>489091</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6720083</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>130800683</v>
+      </c>
+      <c r="B56" t="n">
+        <v>79219</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Skinnaråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>489169</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6720075</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>130800691</v>
+      </c>
+      <c r="B57" t="n">
+        <v>79219</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Skinnaråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>489214</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6720016</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>130800702</v>
+      </c>
+      <c r="B58" t="n">
+        <v>79219</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Skinnaråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>489258</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6719949</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>130800768</v>
+      </c>
+      <c r="B59" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Skinnaråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>489234</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6719934</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>130800619</v>
+      </c>
+      <c r="B60" t="n">
+        <v>57859</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Skinnaråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>489184</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6720170</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>10:08</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>10:08</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>130800708</v>
+      </c>
+      <c r="B61" t="n">
+        <v>79219</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Skinnaråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>489077</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6720065</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>130800604</v>
+      </c>
+      <c r="B62" t="n">
+        <v>5197</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Skinnaråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>489244</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6719935</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>130800705</v>
+      </c>
+      <c r="B63" t="n">
+        <v>79219</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Skinnaråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>489144</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6719996</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>130800674</v>
+      </c>
+      <c r="B64" t="n">
+        <v>79219</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Skinnaråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>489168</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6720197</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>130800665</v>
+      </c>
+      <c r="B65" t="n">
+        <v>79219</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Skinnaråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>489208</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6720188</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>130800694</v>
+      </c>
+      <c r="B66" t="n">
+        <v>79219</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Skinnaråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>489214</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6719991</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>130800692</v>
+      </c>
+      <c r="B67" t="n">
+        <v>79219</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Skinnaråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>489211</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6720011</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>130800620</v>
+      </c>
+      <c r="B68" t="n">
+        <v>57859</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Skinnaråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>489144</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6720087</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>130800711</v>
+      </c>
+      <c r="B69" t="n">
+        <v>79219</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Skinnaråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>489138</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6720109</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 62861-2025 artfynd.xlsx
+++ b/artfynd/A 62861-2025 artfynd.xlsx
@@ -1253,7 +1253,7 @@
         <v>130800713</v>
       </c>
       <c r="B7" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>130800726</v>
       </c>
       <c r="B8" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1464,10 +1464,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130800706</v>
+        <v>130800627</v>
       </c>
       <c r="B9" t="n">
-        <v>79219</v>
+        <v>57860</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1475,34 +1475,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>489143</v>
+        <v>489163</v>
       </c>
       <c r="R9" t="n">
-        <v>6720009</v>
+        <v>6719987</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1534,7 +1539,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1549,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,10 +1576,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130800693</v>
+        <v>130800622</v>
       </c>
       <c r="B10" t="n">
-        <v>79219</v>
+        <v>57860</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1582,34 +1587,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>489211</v>
+        <v>489171</v>
       </c>
       <c r="R10" t="n">
-        <v>6720001</v>
+        <v>6720048</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1641,7 +1651,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1651,7 +1661,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1678,10 +1688,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130800627</v>
+        <v>130800706</v>
       </c>
       <c r="B11" t="n">
-        <v>57859</v>
+        <v>79220</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1689,39 +1699,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>489163</v>
+        <v>489143</v>
       </c>
       <c r="R11" t="n">
-        <v>6719987</v>
+        <v>6720009</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1753,7 +1758,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1763,7 +1768,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1790,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130800672</v>
+        <v>130800693</v>
       </c>
       <c r="B12" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1825,10 +1830,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>489170</v>
+        <v>489211</v>
       </c>
       <c r="R12" t="n">
-        <v>6720188</v>
+        <v>6720001</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1860,7 +1865,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1870,7 +1875,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1897,10 +1902,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130800622</v>
+        <v>130800672</v>
       </c>
       <c r="B13" t="n">
-        <v>57859</v>
+        <v>79220</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1908,39 +1913,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>489171</v>
+        <v>489170</v>
       </c>
       <c r="R13" t="n">
-        <v>6720048</v>
+        <v>6720188</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1972,7 +1972,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2012,7 +2012,7 @@
         <v>130800721</v>
       </c>
       <c r="B14" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2116,50 +2116,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130800641</v>
+        <v>130800671</v>
       </c>
       <c r="B15" t="n">
-        <v>8451</v>
+        <v>79220</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>489210</v>
+        <v>489159</v>
       </c>
       <c r="R15" t="n">
-        <v>6720036</v>
+        <v>6720170</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2191,7 +2186,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2201,7 +2196,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2210,7 +2205,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2229,10 +2223,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130800671</v>
+        <v>130800689</v>
       </c>
       <c r="B16" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2264,10 +2258,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>489159</v>
+        <v>489171</v>
       </c>
       <c r="R16" t="n">
-        <v>6720170</v>
+        <v>6720037</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2299,7 +2293,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2309,7 +2303,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2336,7 +2330,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130800634</v>
+        <v>130800641</v>
       </c>
       <c r="B17" t="n">
         <v>8451</v>
@@ -2376,10 +2370,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>489196</v>
+        <v>489210</v>
       </c>
       <c r="R17" t="n">
-        <v>6720103</v>
+        <v>6720036</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2411,7 +2405,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2421,7 +2415,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2449,45 +2443,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130800689</v>
+        <v>130800634</v>
       </c>
       <c r="B18" t="n">
-        <v>79219</v>
+        <v>8451</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>489171</v>
+        <v>489196</v>
       </c>
       <c r="R18" t="n">
-        <v>6720037</v>
+        <v>6720103</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2519,7 +2518,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2529,7 +2528,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2538,6 +2537,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2559,7 +2559,7 @@
         <v>130800609</v>
       </c>
       <c r="B19" t="n">
-        <v>91774</v>
+        <v>91775</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2663,10 +2663,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130800621</v>
+        <v>130800710</v>
       </c>
       <c r="B20" t="n">
-        <v>57859</v>
+        <v>79220</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2674,39 +2674,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>489175</v>
+        <v>489124</v>
       </c>
       <c r="R20" t="n">
-        <v>6720065</v>
+        <v>6720109</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2738,7 +2733,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2748,7 +2743,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2775,10 +2770,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130800710</v>
+        <v>130800668</v>
       </c>
       <c r="B21" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2810,10 +2805,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>489124</v>
+        <v>489197</v>
       </c>
       <c r="R21" t="n">
-        <v>6720109</v>
+        <v>6720167</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2845,7 +2840,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2855,7 +2850,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2882,10 +2877,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130800668</v>
+        <v>130800621</v>
       </c>
       <c r="B22" t="n">
-        <v>79219</v>
+        <v>57860</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2893,34 +2888,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>489197</v>
+        <v>489175</v>
       </c>
       <c r="R22" t="n">
-        <v>6720167</v>
+        <v>6720065</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2952,7 +2952,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2992,7 +2992,7 @@
         <v>130800690</v>
       </c>
       <c r="B23" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         <v>130800718</v>
       </c>
       <c r="B24" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         <v>130800682</v>
       </c>
       <c r="B25" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3310,10 +3310,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130800695</v>
+        <v>130800696</v>
       </c>
       <c r="B26" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3345,10 +3345,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>489231</v>
+        <v>489243</v>
       </c>
       <c r="R26" t="n">
-        <v>6719941</v>
+        <v>6719933</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3380,7 +3380,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3390,7 +3390,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3417,32 +3417,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130800687</v>
+        <v>130800606</v>
       </c>
       <c r="B27" t="n">
-        <v>79219</v>
+        <v>92146</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3452,10 +3452,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>489175</v>
+        <v>489169</v>
       </c>
       <c r="R27" t="n">
-        <v>6720053</v>
+        <v>6720185</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3487,7 +3487,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3524,10 +3524,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130800725</v>
+        <v>130800695</v>
       </c>
       <c r="B28" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>489332</v>
+        <v>489231</v>
       </c>
       <c r="R28" t="n">
-        <v>6720052</v>
+        <v>6719941</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3594,7 +3594,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3604,7 +3604,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3631,32 +3631,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130800606</v>
+        <v>130800687</v>
       </c>
       <c r="B29" t="n">
-        <v>92145</v>
+        <v>79220</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3666,10 +3666,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>489169</v>
+        <v>489175</v>
       </c>
       <c r="R29" t="n">
-        <v>6720185</v>
+        <v>6720053</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3701,7 +3701,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3738,10 +3738,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130800696</v>
+        <v>130800725</v>
       </c>
       <c r="B30" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3773,10 +3773,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>489243</v>
+        <v>489332</v>
       </c>
       <c r="R30" t="n">
-        <v>6719933</v>
+        <v>6720052</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3808,7 +3808,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3818,7 +3818,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3848,7 +3848,7 @@
         <v>130800688</v>
       </c>
       <c r="B31" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>130800678</v>
       </c>
       <c r="B32" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4062,7 +4062,7 @@
         <v>130800716</v>
       </c>
       <c r="B33" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         <v>130800669</v>
       </c>
       <c r="B34" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4276,7 +4276,7 @@
         <v>130800712</v>
       </c>
       <c r="B35" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4383,7 +4383,7 @@
         <v>130800679</v>
       </c>
       <c r="B36" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4490,7 +4490,7 @@
         <v>130800676</v>
       </c>
       <c r="B37" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
         <v>130800666</v>
       </c>
       <c r="B38" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4704,7 +4704,7 @@
         <v>130800608</v>
       </c>
       <c r="B39" t="n">
-        <v>92145</v>
+        <v>92146</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4811,7 +4811,7 @@
         <v>130800714</v>
       </c>
       <c r="B40" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4918,7 +4918,7 @@
         <v>130800707</v>
       </c>
       <c r="B41" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         <v>130800677</v>
       </c>
       <c r="B42" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5132,7 +5132,7 @@
         <v>130800681</v>
       </c>
       <c r="B43" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5239,7 +5239,7 @@
         <v>130800684</v>
       </c>
       <c r="B44" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5346,7 +5346,7 @@
         <v>130800709</v>
       </c>
       <c r="B45" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5453,7 +5453,7 @@
         <v>130800667</v>
       </c>
       <c r="B46" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5560,7 +5560,7 @@
         <v>130800722</v>
       </c>
       <c r="B47" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5664,10 +5664,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130800610</v>
+        <v>130800704</v>
       </c>
       <c r="B48" t="n">
-        <v>91774</v>
+        <v>79220</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5675,21 +5675,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5699,10 +5699,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>489216</v>
+        <v>489180</v>
       </c>
       <c r="R48" t="n">
-        <v>6719995</v>
+        <v>6719972</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5734,7 +5734,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5744,7 +5744,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5771,10 +5771,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130800704</v>
+        <v>130800715</v>
       </c>
       <c r="B49" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5806,10 +5806,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>489180</v>
+        <v>489166</v>
       </c>
       <c r="R49" t="n">
-        <v>6719972</v>
+        <v>6720127</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5841,7 +5841,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5878,10 +5878,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130800715</v>
+        <v>130800610</v>
       </c>
       <c r="B50" t="n">
-        <v>79219</v>
+        <v>91775</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5889,21 +5889,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5913,10 +5913,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>489166</v>
+        <v>489216</v>
       </c>
       <c r="R50" t="n">
-        <v>6720127</v>
+        <v>6719995</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5948,7 +5948,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5988,7 +5988,7 @@
         <v>130800630</v>
       </c>
       <c r="B51" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6100,7 +6100,7 @@
         <v>130800673</v>
       </c>
       <c r="B52" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6207,7 +6207,7 @@
         <v>130800675</v>
       </c>
       <c r="B53" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6314,7 +6314,7 @@
         <v>130800680</v>
       </c>
       <c r="B54" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6418,50 +6418,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130800637</v>
+        <v>130800683</v>
       </c>
       <c r="B55" t="n">
-        <v>8451</v>
+        <v>79220</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>489091</v>
+        <v>489169</v>
       </c>
       <c r="R55" t="n">
-        <v>6720083</v>
+        <v>6720075</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6493,7 +6488,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6503,7 +6498,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6512,7 +6507,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6531,45 +6525,50 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130800683</v>
+        <v>130800637</v>
       </c>
       <c r="B56" t="n">
-        <v>79219</v>
+        <v>8451</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>489169</v>
+        <v>489091</v>
       </c>
       <c r="R56" t="n">
-        <v>6720075</v>
+        <v>6720083</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6601,7 +6600,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6611,7 +6610,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6620,6 +6619,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6641,7 +6641,7 @@
         <v>130800691</v>
       </c>
       <c r="B57" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6748,7 +6748,7 @@
         <v>130800702</v>
       </c>
       <c r="B58" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6852,50 +6852,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130800768</v>
+        <v>130800708</v>
       </c>
       <c r="B59" t="n">
-        <v>5177</v>
+        <v>79220</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>489234</v>
+        <v>489077</v>
       </c>
       <c r="R59" t="n">
-        <v>6719934</v>
+        <v>6720065</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6927,7 +6922,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6937,7 +6932,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6964,10 +6959,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130800619</v>
+        <v>130800705</v>
       </c>
       <c r="B60" t="n">
-        <v>57859</v>
+        <v>79220</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6975,39 +6970,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>489184</v>
+        <v>489144</v>
       </c>
       <c r="R60" t="n">
-        <v>6720170</v>
+        <v>6719996</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7039,7 +7029,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7049,7 +7039,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7076,10 +7066,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130800708</v>
+        <v>130800619</v>
       </c>
       <c r="B61" t="n">
-        <v>79219</v>
+        <v>57860</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7087,34 +7077,39 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>489077</v>
+        <v>489184</v>
       </c>
       <c r="R61" t="n">
-        <v>6720065</v>
+        <v>6720170</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7146,7 +7141,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7156,7 +7151,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7183,10 +7178,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130800604</v>
+        <v>130800768</v>
       </c>
       <c r="B62" t="n">
-        <v>5197</v>
+        <v>5177</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7194,27 +7189,27 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -7223,10 +7218,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>489244</v>
+        <v>489234</v>
       </c>
       <c r="R62" t="n">
-        <v>6719935</v>
+        <v>6719934</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7258,7 +7253,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7268,7 +7263,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7295,45 +7290,50 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130800705</v>
+        <v>130800604</v>
       </c>
       <c r="B63" t="n">
-        <v>79219</v>
+        <v>5197</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>105930</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>489144</v>
+        <v>489244</v>
       </c>
       <c r="R63" t="n">
-        <v>6719996</v>
+        <v>6719935</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7365,7 +7365,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7375,7 +7375,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7405,7 +7405,7 @@
         <v>130800674</v>
       </c>
       <c r="B64" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7512,7 +7512,7 @@
         <v>130800665</v>
       </c>
       <c r="B65" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7619,7 +7619,7 @@
         <v>130800694</v>
       </c>
       <c r="B66" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7726,7 +7726,7 @@
         <v>130800692</v>
       </c>
       <c r="B67" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7830,10 +7830,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130800620</v>
+        <v>130800711</v>
       </c>
       <c r="B68" t="n">
-        <v>57859</v>
+        <v>79220</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7841,39 +7841,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>489144</v>
+        <v>489138</v>
       </c>
       <c r="R68" t="n">
-        <v>6720087</v>
+        <v>6720109</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7905,7 +7900,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7915,7 +7910,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7942,10 +7937,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130800711</v>
+        <v>130800620</v>
       </c>
       <c r="B69" t="n">
-        <v>79219</v>
+        <v>57860</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7953,34 +7948,39 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>489138</v>
+        <v>489144</v>
       </c>
       <c r="R69" t="n">
-        <v>6720109</v>
+        <v>6720087</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8012,7 +8012,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8022,7 +8022,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD69" t="b">

--- a/artfynd/A 62861-2025 artfynd.xlsx
+++ b/artfynd/A 62861-2025 artfynd.xlsx
@@ -1253,7 +1253,7 @@
         <v>130800713</v>
       </c>
       <c r="B7" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>130800726</v>
       </c>
       <c r="B8" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1464,10 +1464,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130800627</v>
+        <v>130800706</v>
       </c>
       <c r="B9" t="n">
-        <v>57860</v>
+        <v>79221</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1475,39 +1475,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>489163</v>
+        <v>489143</v>
       </c>
       <c r="R9" t="n">
-        <v>6719987</v>
+        <v>6720009</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1539,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1549,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1576,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130800622</v>
+        <v>130800693</v>
       </c>
       <c r="B10" t="n">
-        <v>57860</v>
+        <v>79221</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,39 +1582,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>489171</v>
+        <v>489211</v>
       </c>
       <c r="R10" t="n">
-        <v>6720048</v>
+        <v>6720001</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1651,7 +1641,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1661,7 +1651,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1688,10 +1678,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130800706</v>
+        <v>130800672</v>
       </c>
       <c r="B11" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1723,10 +1713,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>489143</v>
+        <v>489170</v>
       </c>
       <c r="R11" t="n">
-        <v>6720009</v>
+        <v>6720188</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1758,7 +1748,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1768,7 +1758,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,10 +1785,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130800693</v>
+        <v>130800721</v>
       </c>
       <c r="B12" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1830,10 +1820,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>489211</v>
+        <v>489189</v>
       </c>
       <c r="R12" t="n">
-        <v>6720001</v>
+        <v>6720073</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1865,7 +1855,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1875,7 +1865,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1902,10 +1892,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130800672</v>
+        <v>130800627</v>
       </c>
       <c r="B13" t="n">
-        <v>79220</v>
+        <v>57861</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1913,34 +1903,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>489170</v>
+        <v>489163</v>
       </c>
       <c r="R13" t="n">
-        <v>6720188</v>
+        <v>6719987</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1972,7 +1967,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1982,7 +1977,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2009,10 +2004,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130800721</v>
+        <v>130800622</v>
       </c>
       <c r="B14" t="n">
-        <v>79220</v>
+        <v>57861</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2020,34 +2015,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>489189</v>
+        <v>489171</v>
       </c>
       <c r="R14" t="n">
-        <v>6720073</v>
+        <v>6720048</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2079,7 +2079,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2116,10 +2116,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130800671</v>
+        <v>130800609</v>
       </c>
       <c r="B15" t="n">
-        <v>79220</v>
+        <v>91776</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2127,21 +2127,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2151,10 +2151,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>489159</v>
+        <v>489172</v>
       </c>
       <c r="R15" t="n">
-        <v>6720170</v>
+        <v>6720186</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2223,10 +2223,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130800689</v>
+        <v>130800671</v>
       </c>
       <c r="B16" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2258,10 +2258,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>489171</v>
+        <v>489159</v>
       </c>
       <c r="R16" t="n">
-        <v>6720037</v>
+        <v>6720170</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2293,7 +2293,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2330,50 +2330,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130800641</v>
+        <v>130800689</v>
       </c>
       <c r="B17" t="n">
-        <v>8451</v>
+        <v>79221</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>489210</v>
+        <v>489171</v>
       </c>
       <c r="R17" t="n">
-        <v>6720036</v>
+        <v>6720037</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2405,7 +2400,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2415,7 +2410,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2424,7 +2419,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2443,7 +2437,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130800634</v>
+        <v>130800641</v>
       </c>
       <c r="B18" t="n">
         <v>8451</v>
@@ -2483,10 +2477,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>489196</v>
+        <v>489210</v>
       </c>
       <c r="R18" t="n">
-        <v>6720103</v>
+        <v>6720036</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2518,7 +2512,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2528,7 +2522,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2556,45 +2550,50 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130800609</v>
+        <v>130800634</v>
       </c>
       <c r="B19" t="n">
-        <v>91775</v>
+        <v>8451</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>489172</v>
+        <v>489196</v>
       </c>
       <c r="R19" t="n">
-        <v>6720186</v>
+        <v>6720103</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2626,7 +2625,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2636,7 +2635,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2645,6 +2644,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2666,7 +2666,7 @@
         <v>130800710</v>
       </c>
       <c r="B20" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
         <v>130800668</v>
       </c>
       <c r="B21" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         <v>130800621</v>
       </c>
       <c r="B22" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         <v>130800690</v>
       </c>
       <c r="B23" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         <v>130800718</v>
       </c>
       <c r="B24" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         <v>130800682</v>
       </c>
       <c r="B25" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3310,32 +3310,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130800696</v>
+        <v>130800606</v>
       </c>
       <c r="B26" t="n">
-        <v>79220</v>
+        <v>92147</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3345,10 +3345,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>489243</v>
+        <v>489169</v>
       </c>
       <c r="R26" t="n">
-        <v>6719933</v>
+        <v>6720185</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3380,7 +3380,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3390,7 +3390,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3417,32 +3417,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130800606</v>
+        <v>130800695</v>
       </c>
       <c r="B27" t="n">
-        <v>92146</v>
+        <v>79221</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3452,10 +3452,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>489169</v>
+        <v>489231</v>
       </c>
       <c r="R27" t="n">
-        <v>6720185</v>
+        <v>6719941</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3487,7 +3487,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3524,10 +3524,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130800695</v>
+        <v>130800687</v>
       </c>
       <c r="B28" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>489231</v>
+        <v>489175</v>
       </c>
       <c r="R28" t="n">
-        <v>6719941</v>
+        <v>6720053</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3594,7 +3594,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3604,7 +3604,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3631,10 +3631,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130800687</v>
+        <v>130800725</v>
       </c>
       <c r="B29" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3666,10 +3666,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>489175</v>
+        <v>489332</v>
       </c>
       <c r="R29" t="n">
-        <v>6720053</v>
+        <v>6720052</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3701,7 +3701,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3738,10 +3738,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130800725</v>
+        <v>130800696</v>
       </c>
       <c r="B30" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3773,10 +3773,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>489332</v>
+        <v>489243</v>
       </c>
       <c r="R30" t="n">
-        <v>6720052</v>
+        <v>6719933</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3808,7 +3808,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3818,7 +3818,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3848,7 +3848,7 @@
         <v>130800688</v>
       </c>
       <c r="B31" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>130800678</v>
       </c>
       <c r="B32" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4062,7 +4062,7 @@
         <v>130800716</v>
       </c>
       <c r="B33" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         <v>130800669</v>
       </c>
       <c r="B34" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4276,7 +4276,7 @@
         <v>130800712</v>
       </c>
       <c r="B35" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4383,7 +4383,7 @@
         <v>130800679</v>
       </c>
       <c r="B36" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4490,7 +4490,7 @@
         <v>130800676</v>
       </c>
       <c r="B37" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
         <v>130800666</v>
       </c>
       <c r="B38" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4704,7 +4704,7 @@
         <v>130800608</v>
       </c>
       <c r="B39" t="n">
-        <v>92146</v>
+        <v>92147</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4811,7 +4811,7 @@
         <v>130800714</v>
       </c>
       <c r="B40" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4918,7 +4918,7 @@
         <v>130800707</v>
       </c>
       <c r="B41" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         <v>130800677</v>
       </c>
       <c r="B42" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5132,7 +5132,7 @@
         <v>130800681</v>
       </c>
       <c r="B43" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5239,7 +5239,7 @@
         <v>130800684</v>
       </c>
       <c r="B44" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5346,7 +5346,7 @@
         <v>130800709</v>
       </c>
       <c r="B45" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5453,7 +5453,7 @@
         <v>130800667</v>
       </c>
       <c r="B46" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5560,7 +5560,7 @@
         <v>130800722</v>
       </c>
       <c r="B47" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5664,10 +5664,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130800704</v>
+        <v>130800610</v>
       </c>
       <c r="B48" t="n">
-        <v>79220</v>
+        <v>91776</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5675,21 +5675,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5699,10 +5699,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>489180</v>
+        <v>489216</v>
       </c>
       <c r="R48" t="n">
-        <v>6719972</v>
+        <v>6719995</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5734,7 +5734,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5744,7 +5744,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5771,10 +5771,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130800715</v>
+        <v>130800704</v>
       </c>
       <c r="B49" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5806,10 +5806,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>489166</v>
+        <v>489180</v>
       </c>
       <c r="R49" t="n">
-        <v>6720127</v>
+        <v>6719972</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5841,7 +5841,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5878,10 +5878,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130800610</v>
+        <v>130800715</v>
       </c>
       <c r="B50" t="n">
-        <v>91775</v>
+        <v>79221</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5889,21 +5889,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5913,10 +5913,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>489216</v>
+        <v>489166</v>
       </c>
       <c r="R50" t="n">
-        <v>6719995</v>
+        <v>6720127</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5948,7 +5948,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5988,7 +5988,7 @@
         <v>130800630</v>
       </c>
       <c r="B51" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6100,7 +6100,7 @@
         <v>130800673</v>
       </c>
       <c r="B52" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6207,7 +6207,7 @@
         <v>130800675</v>
       </c>
       <c r="B53" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6314,7 +6314,7 @@
         <v>130800680</v>
       </c>
       <c r="B54" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6421,7 +6421,7 @@
         <v>130800683</v>
       </c>
       <c r="B55" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6638,10 +6638,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130800691</v>
+        <v>130800619</v>
       </c>
       <c r="B57" t="n">
-        <v>79220</v>
+        <v>57861</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6649,34 +6649,39 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>489214</v>
+        <v>489184</v>
       </c>
       <c r="R57" t="n">
-        <v>6720016</v>
+        <v>6720170</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6708,7 +6713,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6718,7 +6723,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6745,10 +6750,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130800702</v>
+        <v>130800691</v>
       </c>
       <c r="B58" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6780,10 +6785,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>489258</v>
+        <v>489214</v>
       </c>
       <c r="R58" t="n">
-        <v>6719949</v>
+        <v>6720016</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6815,7 +6820,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6825,7 +6830,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6852,10 +6857,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130800708</v>
+        <v>130800702</v>
       </c>
       <c r="B59" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6887,10 +6892,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>489077</v>
+        <v>489258</v>
       </c>
       <c r="R59" t="n">
-        <v>6720065</v>
+        <v>6719949</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6922,7 +6927,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6932,7 +6937,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6959,10 +6964,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130800705</v>
+        <v>130800708</v>
       </c>
       <c r="B60" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6994,10 +6999,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>489144</v>
+        <v>489077</v>
       </c>
       <c r="R60" t="n">
-        <v>6719996</v>
+        <v>6720065</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7029,7 +7034,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7039,7 +7044,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7066,10 +7071,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130800619</v>
+        <v>130800705</v>
       </c>
       <c r="B61" t="n">
-        <v>57860</v>
+        <v>79221</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7077,39 +7082,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>489184</v>
+        <v>489144</v>
       </c>
       <c r="R61" t="n">
-        <v>6720170</v>
+        <v>6719996</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7141,7 +7141,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7151,7 +7151,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7405,7 +7405,7 @@
         <v>130800674</v>
       </c>
       <c r="B64" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7512,7 +7512,7 @@
         <v>130800665</v>
       </c>
       <c r="B65" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7619,7 +7619,7 @@
         <v>130800694</v>
       </c>
       <c r="B66" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7726,7 +7726,7 @@
         <v>130800692</v>
       </c>
       <c r="B67" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7833,7 +7833,7 @@
         <v>130800711</v>
       </c>
       <c r="B68" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7940,7 +7940,7 @@
         <v>130800620</v>
       </c>
       <c r="B69" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 62861-2025 artfynd.xlsx
+++ b/artfynd/A 62861-2025 artfynd.xlsx
@@ -1464,10 +1464,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130800706</v>
+        <v>130800627</v>
       </c>
       <c r="B9" t="n">
-        <v>79221</v>
+        <v>57861</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1475,34 +1475,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>489143</v>
+        <v>489163</v>
       </c>
       <c r="R9" t="n">
-        <v>6720009</v>
+        <v>6719987</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1534,7 +1539,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1549,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,10 +1576,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130800693</v>
+        <v>130800622</v>
       </c>
       <c r="B10" t="n">
-        <v>79221</v>
+        <v>57861</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1582,34 +1587,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>489211</v>
+        <v>489171</v>
       </c>
       <c r="R10" t="n">
-        <v>6720001</v>
+        <v>6720048</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1641,7 +1651,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1651,7 +1661,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1678,7 +1688,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130800672</v>
+        <v>130800706</v>
       </c>
       <c r="B11" t="n">
         <v>79221</v>
@@ -1713,10 +1723,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>489170</v>
+        <v>489143</v>
       </c>
       <c r="R11" t="n">
-        <v>6720188</v>
+        <v>6720009</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1748,7 +1758,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1758,7 +1768,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1785,7 +1795,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130800721</v>
+        <v>130800693</v>
       </c>
       <c r="B12" t="n">
         <v>79221</v>
@@ -1820,10 +1830,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>489189</v>
+        <v>489211</v>
       </c>
       <c r="R12" t="n">
-        <v>6720073</v>
+        <v>6720001</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1855,7 +1865,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1865,7 +1875,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1892,10 +1902,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130800627</v>
+        <v>130800672</v>
       </c>
       <c r="B13" t="n">
-        <v>57861</v>
+        <v>79221</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1903,39 +1913,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>489163</v>
+        <v>489170</v>
       </c>
       <c r="R13" t="n">
-        <v>6719987</v>
+        <v>6720188</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1967,7 +1972,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1977,7 +1982,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2004,10 +2009,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130800622</v>
+        <v>130800721</v>
       </c>
       <c r="B14" t="n">
-        <v>57861</v>
+        <v>79221</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2015,39 +2020,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>489171</v>
+        <v>489189</v>
       </c>
       <c r="R14" t="n">
-        <v>6720048</v>
+        <v>6720073</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2079,7 +2079,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -3310,32 +3310,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130800606</v>
+        <v>130800695</v>
       </c>
       <c r="B26" t="n">
-        <v>92147</v>
+        <v>79221</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3345,10 +3345,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>489169</v>
+        <v>489231</v>
       </c>
       <c r="R26" t="n">
-        <v>6720185</v>
+        <v>6719941</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3380,7 +3380,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3390,7 +3390,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3417,7 +3417,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130800695</v>
+        <v>130800687</v>
       </c>
       <c r="B27" t="n">
         <v>79221</v>
@@ -3452,10 +3452,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>489231</v>
+        <v>489175</v>
       </c>
       <c r="R27" t="n">
-        <v>6719941</v>
+        <v>6720053</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3487,7 +3487,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3524,7 +3524,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130800687</v>
+        <v>130800725</v>
       </c>
       <c r="B28" t="n">
         <v>79221</v>
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>489175</v>
+        <v>489332</v>
       </c>
       <c r="R28" t="n">
-        <v>6720053</v>
+        <v>6720052</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3594,7 +3594,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3604,7 +3604,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3631,7 +3631,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130800725</v>
+        <v>130800696</v>
       </c>
       <c r="B29" t="n">
         <v>79221</v>
@@ -3666,10 +3666,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>489332</v>
+        <v>489243</v>
       </c>
       <c r="R29" t="n">
-        <v>6720052</v>
+        <v>6719933</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3701,7 +3701,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3738,32 +3738,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130800696</v>
+        <v>130800606</v>
       </c>
       <c r="B30" t="n">
-        <v>79221</v>
+        <v>92147</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3773,10 +3773,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>489243</v>
+        <v>489169</v>
       </c>
       <c r="R30" t="n">
-        <v>6719933</v>
+        <v>6720185</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3808,7 +3808,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3818,7 +3818,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -5985,10 +5985,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130800630</v>
+        <v>130800673</v>
       </c>
       <c r="B51" t="n">
-        <v>57861</v>
+        <v>79221</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5996,39 +5996,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>489207</v>
+        <v>489180</v>
       </c>
       <c r="R51" t="n">
-        <v>6720041</v>
+        <v>6720180</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6060,7 +6055,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6070,7 +6065,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6097,10 +6092,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130800673</v>
+        <v>130800630</v>
       </c>
       <c r="B52" t="n">
-        <v>79221</v>
+        <v>57861</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6108,34 +6103,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>489180</v>
+        <v>489207</v>
       </c>
       <c r="R52" t="n">
-        <v>6720180</v>
+        <v>6720041</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6167,7 +6167,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6177,7 +6177,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6750,45 +6750,50 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130800691</v>
+        <v>130800604</v>
       </c>
       <c r="B58" t="n">
-        <v>79221</v>
+        <v>5197</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>105930</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>489214</v>
+        <v>489244</v>
       </c>
       <c r="R58" t="n">
-        <v>6720016</v>
+        <v>6719935</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6820,7 +6825,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6830,7 +6835,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6857,7 +6862,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130800702</v>
+        <v>130800691</v>
       </c>
       <c r="B59" t="n">
         <v>79221</v>
@@ -6892,10 +6897,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>489258</v>
+        <v>489214</v>
       </c>
       <c r="R59" t="n">
-        <v>6719949</v>
+        <v>6720016</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6927,7 +6932,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6937,7 +6942,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6964,7 +6969,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130800708</v>
+        <v>130800702</v>
       </c>
       <c r="B60" t="n">
         <v>79221</v>
@@ -6999,10 +7004,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>489077</v>
+        <v>489258</v>
       </c>
       <c r="R60" t="n">
-        <v>6720065</v>
+        <v>6719949</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7034,7 +7039,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7044,7 +7049,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7071,7 +7076,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130800705</v>
+        <v>130800708</v>
       </c>
       <c r="B61" t="n">
         <v>79221</v>
@@ -7106,10 +7111,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>489144</v>
+        <v>489077</v>
       </c>
       <c r="R61" t="n">
-        <v>6719996</v>
+        <v>6720065</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7141,7 +7146,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7151,7 +7156,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7178,50 +7183,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130800768</v>
+        <v>130800705</v>
       </c>
       <c r="B62" t="n">
-        <v>5177</v>
+        <v>79221</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>489234</v>
+        <v>489144</v>
       </c>
       <c r="R62" t="n">
-        <v>6719934</v>
+        <v>6719996</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7253,7 +7253,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7263,7 +7263,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7290,10 +7290,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130800604</v>
+        <v>130800768</v>
       </c>
       <c r="B63" t="n">
-        <v>5197</v>
+        <v>5177</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7301,27 +7301,27 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -7330,10 +7330,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>489244</v>
+        <v>489234</v>
       </c>
       <c r="R63" t="n">
-        <v>6719935</v>
+        <v>6719934</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7365,7 +7365,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7375,7 +7375,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7830,10 +7830,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130800711</v>
+        <v>130800620</v>
       </c>
       <c r="B68" t="n">
-        <v>79221</v>
+        <v>57861</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7841,34 +7841,39 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>489138</v>
+        <v>489144</v>
       </c>
       <c r="R68" t="n">
-        <v>6720109</v>
+        <v>6720087</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7900,7 +7905,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7910,7 +7915,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7937,10 +7942,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130800620</v>
+        <v>130800711</v>
       </c>
       <c r="B69" t="n">
-        <v>57861</v>
+        <v>79221</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7948,39 +7953,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>489144</v>
+        <v>489138</v>
       </c>
       <c r="R69" t="n">
-        <v>6720087</v>
+        <v>6720109</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8012,7 +8012,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8022,7 +8022,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD69" t="b">

--- a/artfynd/A 62861-2025 artfynd.xlsx
+++ b/artfynd/A 62861-2025 artfynd.xlsx
@@ -1250,7 +1250,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130800713</v>
+        <v>130800726</v>
       </c>
       <c r="B7" t="n">
         <v>79221</v>
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>489149</v>
+        <v>489323</v>
       </c>
       <c r="R7" t="n">
-        <v>6720123</v>
+        <v>6720025</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,7 +1357,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130800726</v>
+        <v>130800713</v>
       </c>
       <c r="B8" t="n">
         <v>79221</v>
@@ -1392,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>489323</v>
+        <v>489149</v>
       </c>
       <c r="R8" t="n">
-        <v>6720025</v>
+        <v>6720123</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1795,7 +1795,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130800693</v>
+        <v>130800721</v>
       </c>
       <c r="B12" t="n">
         <v>79221</v>
@@ -1830,10 +1830,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>489211</v>
+        <v>489189</v>
       </c>
       <c r="R12" t="n">
-        <v>6720001</v>
+        <v>6720073</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1865,7 +1865,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1902,7 +1902,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130800672</v>
+        <v>130800693</v>
       </c>
       <c r="B13" t="n">
         <v>79221</v>
@@ -1937,10 +1937,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>489170</v>
+        <v>489211</v>
       </c>
       <c r="R13" t="n">
-        <v>6720188</v>
+        <v>6720001</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1972,7 +1972,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2009,7 +2009,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130800721</v>
+        <v>130800672</v>
       </c>
       <c r="B14" t="n">
         <v>79221</v>
@@ -2044,10 +2044,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>489189</v>
+        <v>489170</v>
       </c>
       <c r="R14" t="n">
-        <v>6720073</v>
+        <v>6720188</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2079,7 +2079,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2116,10 +2116,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130800609</v>
+        <v>130800671</v>
       </c>
       <c r="B15" t="n">
-        <v>91776</v>
+        <v>79221</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2127,21 +2127,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2151,10 +2151,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>489172</v>
+        <v>489159</v>
       </c>
       <c r="R15" t="n">
-        <v>6720186</v>
+        <v>6720170</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2223,10 +2223,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130800671</v>
+        <v>130800609</v>
       </c>
       <c r="B16" t="n">
-        <v>79221</v>
+        <v>91776</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2234,21 +2234,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2258,10 +2258,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>489159</v>
+        <v>489172</v>
       </c>
       <c r="R16" t="n">
-        <v>6720170</v>
+        <v>6720186</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2293,7 +2293,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -3524,32 +3524,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130800725</v>
+        <v>130800606</v>
       </c>
       <c r="B28" t="n">
-        <v>79221</v>
+        <v>92147</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>489332</v>
+        <v>489169</v>
       </c>
       <c r="R28" t="n">
-        <v>6720052</v>
+        <v>6720185</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3594,7 +3594,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3604,7 +3604,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3631,7 +3631,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130800696</v>
+        <v>130800725</v>
       </c>
       <c r="B29" t="n">
         <v>79221</v>
@@ -3666,10 +3666,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>489243</v>
+        <v>489332</v>
       </c>
       <c r="R29" t="n">
-        <v>6719933</v>
+        <v>6720052</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3701,7 +3701,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3738,32 +3738,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130800606</v>
+        <v>130800696</v>
       </c>
       <c r="B30" t="n">
-        <v>92147</v>
+        <v>79221</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3773,10 +3773,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>489169</v>
+        <v>489243</v>
       </c>
       <c r="R30" t="n">
-        <v>6720185</v>
+        <v>6719933</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3808,7 +3808,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3818,7 +3818,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4380,7 +4380,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130800679</v>
+        <v>130800676</v>
       </c>
       <c r="B36" t="n">
         <v>79221</v>
@@ -4415,10 +4415,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>489122</v>
+        <v>489151</v>
       </c>
       <c r="R36" t="n">
-        <v>6720120</v>
+        <v>6720144</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4450,7 +4450,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4460,7 +4460,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4487,7 +4487,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130800676</v>
+        <v>130800666</v>
       </c>
       <c r="B37" t="n">
         <v>79221</v>
@@ -4522,10 +4522,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>489151</v>
+        <v>489208</v>
       </c>
       <c r="R37" t="n">
-        <v>6720144</v>
+        <v>6720174</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4557,7 +4557,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4567,7 +4567,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4594,7 +4594,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130800666</v>
+        <v>130800679</v>
       </c>
       <c r="B38" t="n">
         <v>79221</v>
@@ -4629,10 +4629,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>489208</v>
+        <v>489122</v>
       </c>
       <c r="R38" t="n">
-        <v>6720174</v>
+        <v>6720120</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4664,7 +4664,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4674,7 +4674,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4701,32 +4701,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130800608</v>
+        <v>130800714</v>
       </c>
       <c r="B39" t="n">
-        <v>92147</v>
+        <v>79221</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4736,10 +4736,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>489214</v>
+        <v>489163</v>
       </c>
       <c r="R39" t="n">
-        <v>6719996</v>
+        <v>6720122</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4771,7 +4771,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4808,7 +4808,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130800714</v>
+        <v>130800707</v>
       </c>
       <c r="B40" t="n">
         <v>79221</v>
@@ -4843,10 +4843,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>489163</v>
+        <v>489119</v>
       </c>
       <c r="R40" t="n">
-        <v>6720122</v>
+        <v>6720040</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4878,7 +4878,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4915,32 +4915,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130800707</v>
+        <v>130800608</v>
       </c>
       <c r="B41" t="n">
-        <v>79221</v>
+        <v>92147</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4950,10 +4950,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>489119</v>
+        <v>489214</v>
       </c>
       <c r="R41" t="n">
-        <v>6720040</v>
+        <v>6719996</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4985,7 +4985,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4995,7 +4995,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5129,7 +5129,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130800681</v>
+        <v>130800684</v>
       </c>
       <c r="B43" t="n">
         <v>79221</v>
@@ -5164,10 +5164,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>489138</v>
+        <v>489177</v>
       </c>
       <c r="R43" t="n">
-        <v>6720092</v>
+        <v>6720066</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5199,7 +5199,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5209,7 +5209,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5236,7 +5236,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130800684</v>
+        <v>130800709</v>
       </c>
       <c r="B44" t="n">
         <v>79221</v>
@@ -5271,10 +5271,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>489177</v>
+        <v>489094</v>
       </c>
       <c r="R44" t="n">
-        <v>6720066</v>
+        <v>6720086</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5343,7 +5343,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130800709</v>
+        <v>130800667</v>
       </c>
       <c r="B45" t="n">
         <v>79221</v>
@@ -5378,10 +5378,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>489094</v>
+        <v>489199</v>
       </c>
       <c r="R45" t="n">
-        <v>6720086</v>
+        <v>6720176</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5423,7 +5423,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5450,7 +5450,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130800667</v>
+        <v>130800681</v>
       </c>
       <c r="B46" t="n">
         <v>79221</v>
@@ -5485,10 +5485,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>489199</v>
+        <v>489138</v>
       </c>
       <c r="R46" t="n">
-        <v>6720176</v>
+        <v>6720092</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5520,7 +5520,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5530,7 +5530,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5664,10 +5664,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130800610</v>
+        <v>130800715</v>
       </c>
       <c r="B48" t="n">
-        <v>91776</v>
+        <v>79221</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5675,21 +5675,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5699,10 +5699,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>489216</v>
+        <v>489166</v>
       </c>
       <c r="R48" t="n">
-        <v>6719995</v>
+        <v>6720127</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5734,7 +5734,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5744,7 +5744,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5771,10 +5771,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130800704</v>
+        <v>130800610</v>
       </c>
       <c r="B49" t="n">
-        <v>79221</v>
+        <v>91776</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5782,21 +5782,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5806,10 +5806,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>489180</v>
+        <v>489216</v>
       </c>
       <c r="R49" t="n">
-        <v>6719972</v>
+        <v>6719995</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5841,7 +5841,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5878,7 +5878,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130800715</v>
+        <v>130800704</v>
       </c>
       <c r="B50" t="n">
         <v>79221</v>
@@ -5913,10 +5913,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>489166</v>
+        <v>489180</v>
       </c>
       <c r="R50" t="n">
-        <v>6720127</v>
+        <v>6719972</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5948,7 +5948,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5985,10 +5985,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130800673</v>
+        <v>130800630</v>
       </c>
       <c r="B51" t="n">
-        <v>79221</v>
+        <v>57861</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5996,34 +5996,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>489180</v>
+        <v>489207</v>
       </c>
       <c r="R51" t="n">
-        <v>6720180</v>
+        <v>6720041</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6055,7 +6060,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6065,7 +6070,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6092,10 +6097,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130800630</v>
+        <v>130800673</v>
       </c>
       <c r="B52" t="n">
-        <v>57861</v>
+        <v>79221</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6103,39 +6108,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>489207</v>
+        <v>489180</v>
       </c>
       <c r="R52" t="n">
-        <v>6720041</v>
+        <v>6720180</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6167,7 +6167,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6177,7 +6177,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6418,45 +6418,50 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130800683</v>
+        <v>130800637</v>
       </c>
       <c r="B55" t="n">
-        <v>79221</v>
+        <v>8451</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>489169</v>
+        <v>489091</v>
       </c>
       <c r="R55" t="n">
-        <v>6720075</v>
+        <v>6720083</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6488,7 +6493,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6498,7 +6503,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6507,6 +6512,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6525,50 +6531,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130800637</v>
+        <v>130800683</v>
       </c>
       <c r="B56" t="n">
-        <v>8451</v>
+        <v>79221</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>489091</v>
+        <v>489169</v>
       </c>
       <c r="R56" t="n">
-        <v>6720083</v>
+        <v>6720075</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6600,7 +6601,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6610,7 +6611,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6619,7 +6620,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6638,10 +6638,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130800619</v>
+        <v>130800702</v>
       </c>
       <c r="B57" t="n">
-        <v>57861</v>
+        <v>79221</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6649,39 +6649,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>489184</v>
+        <v>489258</v>
       </c>
       <c r="R57" t="n">
-        <v>6720170</v>
+        <v>6719949</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6713,7 +6708,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6723,7 +6718,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6750,50 +6745,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130800604</v>
+        <v>130800708</v>
       </c>
       <c r="B58" t="n">
-        <v>5197</v>
+        <v>79221</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>489244</v>
+        <v>489077</v>
       </c>
       <c r="R58" t="n">
-        <v>6719935</v>
+        <v>6720065</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6825,7 +6815,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6835,7 +6825,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6969,7 +6959,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130800702</v>
+        <v>130800705</v>
       </c>
       <c r="B60" t="n">
         <v>79221</v>
@@ -7004,10 +6994,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>489258</v>
+        <v>489144</v>
       </c>
       <c r="R60" t="n">
-        <v>6719949</v>
+        <v>6719996</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7039,7 +7029,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7049,7 +7039,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7076,10 +7066,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130800708</v>
+        <v>130800619</v>
       </c>
       <c r="B61" t="n">
-        <v>79221</v>
+        <v>57861</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7087,34 +7077,39 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>489077</v>
+        <v>489184</v>
       </c>
       <c r="R61" t="n">
-        <v>6720065</v>
+        <v>6720170</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7146,7 +7141,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7156,7 +7151,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7183,45 +7178,50 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130800705</v>
+        <v>130800768</v>
       </c>
       <c r="B62" t="n">
-        <v>79221</v>
+        <v>5177</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>489144</v>
+        <v>489234</v>
       </c>
       <c r="R62" t="n">
-        <v>6719996</v>
+        <v>6719934</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7253,7 +7253,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7263,7 +7263,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7290,10 +7290,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130800768</v>
+        <v>130800604</v>
       </c>
       <c r="B63" t="n">
-        <v>5177</v>
+        <v>5197</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7301,27 +7301,27 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -7330,10 +7330,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>489234</v>
+        <v>489244</v>
       </c>
       <c r="R63" t="n">
-        <v>6719934</v>
+        <v>6719935</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7365,7 +7365,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7375,7 +7375,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7402,7 +7402,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130800674</v>
+        <v>130800692</v>
       </c>
       <c r="B64" t="n">
         <v>79221</v>
@@ -7437,10 +7437,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>489168</v>
+        <v>489211</v>
       </c>
       <c r="R64" t="n">
-        <v>6720197</v>
+        <v>6720011</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7472,7 +7472,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7482,7 +7482,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7723,7 +7723,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130800692</v>
+        <v>130800674</v>
       </c>
       <c r="B67" t="n">
         <v>79221</v>
@@ -7758,10 +7758,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>489211</v>
+        <v>489168</v>
       </c>
       <c r="R67" t="n">
-        <v>6720011</v>
+        <v>6720197</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7793,7 +7793,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7803,7 +7803,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD67" t="b">

--- a/artfynd/A 62861-2025 artfynd.xlsx
+++ b/artfynd/A 62861-2025 artfynd.xlsx
@@ -1688,7 +1688,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130800706</v>
+        <v>130800721</v>
       </c>
       <c r="B11" t="n">
         <v>79221</v>
@@ -1723,10 +1723,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>489143</v>
+        <v>489189</v>
       </c>
       <c r="R11" t="n">
-        <v>6720009</v>
+        <v>6720073</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,7 +1795,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130800721</v>
+        <v>130800706</v>
       </c>
       <c r="B12" t="n">
         <v>79221</v>
@@ -1830,10 +1830,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>489189</v>
+        <v>489143</v>
       </c>
       <c r="R12" t="n">
-        <v>6720073</v>
+        <v>6720009</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1865,7 +1865,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2663,10 +2663,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130800710</v>
+        <v>130800621</v>
       </c>
       <c r="B20" t="n">
-        <v>79221</v>
+        <v>57861</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2674,34 +2674,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>489124</v>
+        <v>489175</v>
       </c>
       <c r="R20" t="n">
-        <v>6720109</v>
+        <v>6720065</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2733,7 +2738,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2743,7 +2748,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2770,7 +2775,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130800668</v>
+        <v>130800710</v>
       </c>
       <c r="B21" t="n">
         <v>79221</v>
@@ -2805,10 +2810,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>489197</v>
+        <v>489124</v>
       </c>
       <c r="R21" t="n">
-        <v>6720167</v>
+        <v>6720109</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2840,7 +2845,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2850,7 +2855,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2877,10 +2882,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130800621</v>
+        <v>130800668</v>
       </c>
       <c r="B22" t="n">
-        <v>57861</v>
+        <v>79221</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2888,39 +2893,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>489175</v>
+        <v>489197</v>
       </c>
       <c r="R22" t="n">
-        <v>6720065</v>
+        <v>6720167</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2952,7 +2952,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -4487,7 +4487,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130800666</v>
+        <v>130800679</v>
       </c>
       <c r="B37" t="n">
         <v>79221</v>
@@ -4522,10 +4522,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>489208</v>
+        <v>489122</v>
       </c>
       <c r="R37" t="n">
-        <v>6720174</v>
+        <v>6720120</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4557,7 +4557,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4567,7 +4567,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4594,7 +4594,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130800679</v>
+        <v>130800666</v>
       </c>
       <c r="B38" t="n">
         <v>79221</v>
@@ -4629,10 +4629,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>489122</v>
+        <v>489208</v>
       </c>
       <c r="R38" t="n">
-        <v>6720120</v>
+        <v>6720174</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4664,7 +4664,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4674,7 +4674,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4701,7 +4701,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130800714</v>
+        <v>130800677</v>
       </c>
       <c r="B39" t="n">
         <v>79221</v>
@@ -4736,10 +4736,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>489163</v>
+        <v>489132</v>
       </c>
       <c r="R39" t="n">
-        <v>6720122</v>
+        <v>6720123</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4771,7 +4771,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4808,7 +4808,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130800707</v>
+        <v>130800714</v>
       </c>
       <c r="B40" t="n">
         <v>79221</v>
@@ -4843,10 +4843,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>489119</v>
+        <v>489163</v>
       </c>
       <c r="R40" t="n">
-        <v>6720040</v>
+        <v>6720122</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4878,7 +4878,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4915,32 +4915,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130800608</v>
+        <v>130800707</v>
       </c>
       <c r="B41" t="n">
-        <v>92147</v>
+        <v>79221</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4950,10 +4950,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>489214</v>
+        <v>489119</v>
       </c>
       <c r="R41" t="n">
-        <v>6719996</v>
+        <v>6720040</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4985,7 +4985,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4995,7 +4995,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5022,32 +5022,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130800677</v>
+        <v>130800608</v>
       </c>
       <c r="B42" t="n">
-        <v>79221</v>
+        <v>92147</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5057,10 +5057,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>489132</v>
+        <v>489214</v>
       </c>
       <c r="R42" t="n">
-        <v>6720123</v>
+        <v>6719996</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5092,7 +5092,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5102,7 +5102,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 62861-2025 artfynd.xlsx
+++ b/artfynd/A 62861-2025 artfynd.xlsx
@@ -1250,7 +1250,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130800726</v>
+        <v>130800713</v>
       </c>
       <c r="B7" t="n">
         <v>79221</v>
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>489323</v>
+        <v>489149</v>
       </c>
       <c r="R7" t="n">
-        <v>6720025</v>
+        <v>6720123</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,7 +1357,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130800713</v>
+        <v>130800726</v>
       </c>
       <c r="B8" t="n">
         <v>79221</v>
@@ -1392,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>489149</v>
+        <v>489323</v>
       </c>
       <c r="R8" t="n">
-        <v>6720123</v>
+        <v>6720025</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1464,10 +1464,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130800627</v>
+        <v>130800706</v>
       </c>
       <c r="B9" t="n">
-        <v>57861</v>
+        <v>79221</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1475,39 +1475,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>489163</v>
+        <v>489143</v>
       </c>
       <c r="R9" t="n">
-        <v>6719987</v>
+        <v>6720009</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1539,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1549,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1576,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130800622</v>
+        <v>130800693</v>
       </c>
       <c r="B10" t="n">
-        <v>57861</v>
+        <v>79221</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,39 +1582,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>489171</v>
+        <v>489211</v>
       </c>
       <c r="R10" t="n">
-        <v>6720048</v>
+        <v>6720001</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1651,7 +1641,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1661,7 +1651,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1688,7 +1678,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130800721</v>
+        <v>130800672</v>
       </c>
       <c r="B11" t="n">
         <v>79221</v>
@@ -1723,10 +1713,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>489189</v>
+        <v>489170</v>
       </c>
       <c r="R11" t="n">
-        <v>6720073</v>
+        <v>6720188</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1758,7 +1748,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1768,7 +1758,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,7 +1785,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130800706</v>
+        <v>130800721</v>
       </c>
       <c r="B12" t="n">
         <v>79221</v>
@@ -1830,10 +1820,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>489143</v>
+        <v>489189</v>
       </c>
       <c r="R12" t="n">
-        <v>6720009</v>
+        <v>6720073</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1865,7 +1855,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1875,7 +1865,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1902,10 +1892,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130800693</v>
+        <v>130800627</v>
       </c>
       <c r="B13" t="n">
-        <v>79221</v>
+        <v>57861</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1913,34 +1903,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>489211</v>
+        <v>489163</v>
       </c>
       <c r="R13" t="n">
-        <v>6720001</v>
+        <v>6719987</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1972,7 +1967,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1982,7 +1977,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2009,10 +2004,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130800672</v>
+        <v>130800622</v>
       </c>
       <c r="B14" t="n">
-        <v>79221</v>
+        <v>57861</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2020,34 +2015,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>489170</v>
+        <v>489171</v>
       </c>
       <c r="R14" t="n">
-        <v>6720188</v>
+        <v>6720048</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2079,7 +2079,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2223,10 +2223,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130800609</v>
+        <v>130800689</v>
       </c>
       <c r="B16" t="n">
-        <v>91776</v>
+        <v>79221</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2234,21 +2234,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2258,10 +2258,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>489172</v>
+        <v>489171</v>
       </c>
       <c r="R16" t="n">
-        <v>6720186</v>
+        <v>6720037</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2293,7 +2293,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2330,10 +2330,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130800689</v>
+        <v>130800609</v>
       </c>
       <c r="B17" t="n">
-        <v>79221</v>
+        <v>91776</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2341,21 +2341,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2365,10 +2365,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>489171</v>
+        <v>489172</v>
       </c>
       <c r="R17" t="n">
-        <v>6720037</v>
+        <v>6720186</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2400,7 +2400,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2663,10 +2663,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130800621</v>
+        <v>130800710</v>
       </c>
       <c r="B20" t="n">
-        <v>57861</v>
+        <v>79221</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2674,39 +2674,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>489175</v>
+        <v>489124</v>
       </c>
       <c r="R20" t="n">
-        <v>6720065</v>
+        <v>6720109</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2738,7 +2733,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2748,7 +2743,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2775,7 +2770,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130800710</v>
+        <v>130800668</v>
       </c>
       <c r="B21" t="n">
         <v>79221</v>
@@ -2810,10 +2805,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>489124</v>
+        <v>489197</v>
       </c>
       <c r="R21" t="n">
-        <v>6720109</v>
+        <v>6720167</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2845,7 +2840,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2855,7 +2850,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2882,10 +2877,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130800668</v>
+        <v>130800621</v>
       </c>
       <c r="B22" t="n">
-        <v>79221</v>
+        <v>57861</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2893,34 +2888,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>489197</v>
+        <v>489175</v>
       </c>
       <c r="R22" t="n">
-        <v>6720167</v>
+        <v>6720065</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2952,7 +2952,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3524,32 +3524,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130800606</v>
+        <v>130800725</v>
       </c>
       <c r="B28" t="n">
-        <v>92147</v>
+        <v>79221</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>489169</v>
+        <v>489332</v>
       </c>
       <c r="R28" t="n">
-        <v>6720185</v>
+        <v>6720052</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3594,7 +3594,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3604,7 +3604,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3631,7 +3631,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130800725</v>
+        <v>130800696</v>
       </c>
       <c r="B29" t="n">
         <v>79221</v>
@@ -3666,10 +3666,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>489332</v>
+        <v>489243</v>
       </c>
       <c r="R29" t="n">
-        <v>6720052</v>
+        <v>6719933</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3701,7 +3701,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3738,32 +3738,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130800696</v>
+        <v>130800606</v>
       </c>
       <c r="B30" t="n">
-        <v>79221</v>
+        <v>92147</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3773,10 +3773,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>489243</v>
+        <v>489169</v>
       </c>
       <c r="R30" t="n">
-        <v>6719933</v>
+        <v>6720185</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3808,7 +3808,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3818,7 +3818,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4380,7 +4380,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130800676</v>
+        <v>130800679</v>
       </c>
       <c r="B36" t="n">
         <v>79221</v>
@@ -4415,10 +4415,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>489151</v>
+        <v>489122</v>
       </c>
       <c r="R36" t="n">
-        <v>6720144</v>
+        <v>6720120</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4450,7 +4450,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4460,7 +4460,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4487,7 +4487,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130800679</v>
+        <v>130800676</v>
       </c>
       <c r="B37" t="n">
         <v>79221</v>
@@ -4522,10 +4522,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>489122</v>
+        <v>489151</v>
       </c>
       <c r="R37" t="n">
-        <v>6720120</v>
+        <v>6720144</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4557,7 +4557,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4567,7 +4567,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4701,32 +4701,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130800677</v>
+        <v>130800608</v>
       </c>
       <c r="B39" t="n">
-        <v>79221</v>
+        <v>92147</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4736,10 +4736,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>489132</v>
+        <v>489214</v>
       </c>
       <c r="R39" t="n">
-        <v>6720123</v>
+        <v>6719996</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4771,7 +4771,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5022,32 +5022,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130800608</v>
+        <v>130800677</v>
       </c>
       <c r="B42" t="n">
-        <v>92147</v>
+        <v>79221</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5057,10 +5057,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>489214</v>
+        <v>489132</v>
       </c>
       <c r="R42" t="n">
-        <v>6719996</v>
+        <v>6720123</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5092,7 +5092,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5102,7 +5102,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5129,7 +5129,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130800684</v>
+        <v>130800681</v>
       </c>
       <c r="B43" t="n">
         <v>79221</v>
@@ -5164,10 +5164,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>489177</v>
+        <v>489138</v>
       </c>
       <c r="R43" t="n">
-        <v>6720066</v>
+        <v>6720092</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5199,7 +5199,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5209,7 +5209,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5236,7 +5236,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130800709</v>
+        <v>130800684</v>
       </c>
       <c r="B44" t="n">
         <v>79221</v>
@@ -5271,10 +5271,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>489094</v>
+        <v>489177</v>
       </c>
       <c r="R44" t="n">
-        <v>6720086</v>
+        <v>6720066</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5343,7 +5343,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130800667</v>
+        <v>130800709</v>
       </c>
       <c r="B45" t="n">
         <v>79221</v>
@@ -5378,10 +5378,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>489199</v>
+        <v>489094</v>
       </c>
       <c r="R45" t="n">
-        <v>6720176</v>
+        <v>6720086</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5423,7 +5423,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5450,7 +5450,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130800681</v>
+        <v>130800667</v>
       </c>
       <c r="B46" t="n">
         <v>79221</v>
@@ -5485,10 +5485,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>489138</v>
+        <v>489199</v>
       </c>
       <c r="R46" t="n">
-        <v>6720092</v>
+        <v>6720176</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5520,7 +5520,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5530,7 +5530,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5664,7 +5664,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130800715</v>
+        <v>130800704</v>
       </c>
       <c r="B48" t="n">
         <v>79221</v>
@@ -5699,10 +5699,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>489166</v>
+        <v>489180</v>
       </c>
       <c r="R48" t="n">
-        <v>6720127</v>
+        <v>6719972</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5734,7 +5734,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5744,7 +5744,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5771,10 +5771,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130800610</v>
+        <v>130800715</v>
       </c>
       <c r="B49" t="n">
-        <v>91776</v>
+        <v>79221</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5782,21 +5782,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5806,10 +5806,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>489216</v>
+        <v>489166</v>
       </c>
       <c r="R49" t="n">
-        <v>6719995</v>
+        <v>6720127</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5841,7 +5841,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5878,10 +5878,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130800704</v>
+        <v>130800610</v>
       </c>
       <c r="B50" t="n">
-        <v>79221</v>
+        <v>91776</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5889,21 +5889,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5913,10 +5913,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>489180</v>
+        <v>489216</v>
       </c>
       <c r="R50" t="n">
-        <v>6719972</v>
+        <v>6719995</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5948,7 +5948,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5985,10 +5985,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130800630</v>
+        <v>130800673</v>
       </c>
       <c r="B51" t="n">
-        <v>57861</v>
+        <v>79221</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5996,39 +5996,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>489207</v>
+        <v>489180</v>
       </c>
       <c r="R51" t="n">
-        <v>6720041</v>
+        <v>6720180</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6060,7 +6055,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6070,7 +6065,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6097,10 +6092,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130800673</v>
+        <v>130800630</v>
       </c>
       <c r="B52" t="n">
-        <v>79221</v>
+        <v>57861</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6108,34 +6103,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>489180</v>
+        <v>489207</v>
       </c>
       <c r="R52" t="n">
-        <v>6720180</v>
+        <v>6720041</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6167,7 +6167,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6177,7 +6177,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6418,50 +6418,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130800637</v>
+        <v>130800683</v>
       </c>
       <c r="B55" t="n">
-        <v>8451</v>
+        <v>79221</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>489091</v>
+        <v>489169</v>
       </c>
       <c r="R55" t="n">
-        <v>6720083</v>
+        <v>6720075</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6493,7 +6488,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6503,7 +6498,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6512,7 +6507,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6531,45 +6525,50 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130800683</v>
+        <v>130800637</v>
       </c>
       <c r="B56" t="n">
-        <v>79221</v>
+        <v>8451</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>489169</v>
+        <v>489091</v>
       </c>
       <c r="R56" t="n">
-        <v>6720075</v>
+        <v>6720083</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6601,7 +6600,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6611,7 +6610,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6620,6 +6619,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6638,10 +6638,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130800702</v>
+        <v>130800619</v>
       </c>
       <c r="B57" t="n">
-        <v>79221</v>
+        <v>57861</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6649,34 +6649,39 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>489258</v>
+        <v>489184</v>
       </c>
       <c r="R57" t="n">
-        <v>6719949</v>
+        <v>6720170</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6708,7 +6713,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6718,7 +6723,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6745,45 +6750,50 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130800708</v>
+        <v>130800768</v>
       </c>
       <c r="B58" t="n">
-        <v>79221</v>
+        <v>5177</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>489077</v>
+        <v>489234</v>
       </c>
       <c r="R58" t="n">
-        <v>6720065</v>
+        <v>6719934</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6815,7 +6825,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6825,7 +6835,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6852,45 +6862,50 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130800691</v>
+        <v>130800604</v>
       </c>
       <c r="B59" t="n">
-        <v>79221</v>
+        <v>5197</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>105930</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>489214</v>
+        <v>489244</v>
       </c>
       <c r="R59" t="n">
-        <v>6720016</v>
+        <v>6719935</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6922,7 +6937,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6932,7 +6947,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6959,7 +6974,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130800705</v>
+        <v>130800691</v>
       </c>
       <c r="B60" t="n">
         <v>79221</v>
@@ -6994,10 +7009,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>489144</v>
+        <v>489214</v>
       </c>
       <c r="R60" t="n">
-        <v>6719996</v>
+        <v>6720016</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7029,7 +7044,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7039,7 +7054,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7066,10 +7081,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130800619</v>
+        <v>130800702</v>
       </c>
       <c r="B61" t="n">
-        <v>57861</v>
+        <v>79221</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7077,39 +7092,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>489184</v>
+        <v>489258</v>
       </c>
       <c r="R61" t="n">
-        <v>6720170</v>
+        <v>6719949</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7141,7 +7151,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7151,7 +7161,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7178,50 +7188,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130800768</v>
+        <v>130800708</v>
       </c>
       <c r="B62" t="n">
-        <v>5177</v>
+        <v>79221</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>489234</v>
+        <v>489077</v>
       </c>
       <c r="R62" t="n">
-        <v>6719934</v>
+        <v>6720065</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7253,7 +7258,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7263,7 +7268,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7290,50 +7295,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130800604</v>
+        <v>130800705</v>
       </c>
       <c r="B63" t="n">
-        <v>5197</v>
+        <v>79221</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>489244</v>
+        <v>489144</v>
       </c>
       <c r="R63" t="n">
-        <v>6719935</v>
+        <v>6719996</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7365,7 +7365,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7375,7 +7375,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7402,7 +7402,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130800692</v>
+        <v>130800674</v>
       </c>
       <c r="B64" t="n">
         <v>79221</v>
@@ -7437,10 +7437,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>489211</v>
+        <v>489168</v>
       </c>
       <c r="R64" t="n">
-        <v>6720011</v>
+        <v>6720197</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7472,7 +7472,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7482,7 +7482,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7723,7 +7723,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130800674</v>
+        <v>130800692</v>
       </c>
       <c r="B67" t="n">
         <v>79221</v>
@@ -7758,10 +7758,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>489168</v>
+        <v>489211</v>
       </c>
       <c r="R67" t="n">
-        <v>6720197</v>
+        <v>6720011</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7793,7 +7793,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7803,7 +7803,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7830,10 +7830,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130800620</v>
+        <v>130800711</v>
       </c>
       <c r="B68" t="n">
-        <v>57861</v>
+        <v>79221</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7841,39 +7841,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>489144</v>
+        <v>489138</v>
       </c>
       <c r="R68" t="n">
-        <v>6720087</v>
+        <v>6720109</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7905,7 +7900,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7915,7 +7910,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7942,10 +7937,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130800711</v>
+        <v>130800620</v>
       </c>
       <c r="B69" t="n">
-        <v>79221</v>
+        <v>57861</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7953,34 +7948,39 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>489138</v>
+        <v>489144</v>
       </c>
       <c r="R69" t="n">
-        <v>6720109</v>
+        <v>6720087</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8012,7 +8012,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8022,7 +8022,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD69" t="b">

--- a/artfynd/A 62861-2025 artfynd.xlsx
+++ b/artfynd/A 62861-2025 artfynd.xlsx
@@ -1892,7 +1892,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130800627</v>
+        <v>130800622</v>
       </c>
       <c r="B13" t="n">
         <v>57861</v>
@@ -1923,7 +1923,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1932,10 +1932,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>489163</v>
+        <v>489171</v>
       </c>
       <c r="R13" t="n">
-        <v>6719987</v>
+        <v>6720048</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1967,7 +1967,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1977,7 +1977,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2004,7 +2004,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130800622</v>
+        <v>130800627</v>
       </c>
       <c r="B14" t="n">
         <v>57861</v>
@@ -2035,7 +2035,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2044,10 +2044,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>489171</v>
+        <v>489163</v>
       </c>
       <c r="R14" t="n">
-        <v>6720048</v>
+        <v>6719987</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2079,7 +2079,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2116,45 +2116,50 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130800671</v>
+        <v>130800641</v>
       </c>
       <c r="B15" t="n">
-        <v>79221</v>
+        <v>8451</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>489159</v>
+        <v>489210</v>
       </c>
       <c r="R15" t="n">
-        <v>6720170</v>
+        <v>6720036</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2186,7 +2191,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2196,7 +2201,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2205,6 +2210,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2223,45 +2229,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130800689</v>
+        <v>130800634</v>
       </c>
       <c r="B16" t="n">
-        <v>79221</v>
+        <v>8451</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>489171</v>
+        <v>489196</v>
       </c>
       <c r="R16" t="n">
-        <v>6720037</v>
+        <v>6720103</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2293,7 +2304,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2303,7 +2314,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2312,6 +2323,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2437,50 +2449,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130800641</v>
+        <v>130800671</v>
       </c>
       <c r="B18" t="n">
-        <v>8451</v>
+        <v>79221</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>489210</v>
+        <v>489159</v>
       </c>
       <c r="R18" t="n">
-        <v>6720036</v>
+        <v>6720170</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2512,7 +2519,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2522,7 +2529,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2531,7 +2538,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2550,50 +2556,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130800634</v>
+        <v>130800689</v>
       </c>
       <c r="B19" t="n">
-        <v>8451</v>
+        <v>79221</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>489196</v>
+        <v>489171</v>
       </c>
       <c r="R19" t="n">
-        <v>6720103</v>
+        <v>6720037</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2625,7 +2626,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2635,7 +2636,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2644,7 +2645,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2663,10 +2663,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130800710</v>
+        <v>130800621</v>
       </c>
       <c r="B20" t="n">
-        <v>79221</v>
+        <v>57861</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2674,34 +2674,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>489124</v>
+        <v>489175</v>
       </c>
       <c r="R20" t="n">
-        <v>6720109</v>
+        <v>6720065</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2733,7 +2738,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2743,7 +2748,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2770,7 +2775,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130800668</v>
+        <v>130800710</v>
       </c>
       <c r="B21" t="n">
         <v>79221</v>
@@ -2805,10 +2810,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>489197</v>
+        <v>489124</v>
       </c>
       <c r="R21" t="n">
-        <v>6720167</v>
+        <v>6720109</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2840,7 +2845,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2850,7 +2855,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2877,10 +2882,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130800621</v>
+        <v>130800668</v>
       </c>
       <c r="B22" t="n">
-        <v>57861</v>
+        <v>79221</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2888,39 +2893,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>489175</v>
+        <v>489197</v>
       </c>
       <c r="R22" t="n">
-        <v>6720065</v>
+        <v>6720167</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2952,7 +2952,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3417,32 +3417,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130800687</v>
+        <v>130800606</v>
       </c>
       <c r="B27" t="n">
-        <v>79221</v>
+        <v>92147</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3452,10 +3452,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>489175</v>
+        <v>489169</v>
       </c>
       <c r="R27" t="n">
-        <v>6720053</v>
+        <v>6720185</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3487,7 +3487,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3524,7 +3524,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130800725</v>
+        <v>130800687</v>
       </c>
       <c r="B28" t="n">
         <v>79221</v>
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>489332</v>
+        <v>489175</v>
       </c>
       <c r="R28" t="n">
-        <v>6720052</v>
+        <v>6720053</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3594,7 +3594,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3604,7 +3604,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3631,7 +3631,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130800696</v>
+        <v>130800725</v>
       </c>
       <c r="B29" t="n">
         <v>79221</v>
@@ -3666,10 +3666,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>489243</v>
+        <v>489332</v>
       </c>
       <c r="R29" t="n">
-        <v>6719933</v>
+        <v>6720052</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3701,7 +3701,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3738,32 +3738,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130800606</v>
+        <v>130800696</v>
       </c>
       <c r="B30" t="n">
-        <v>92147</v>
+        <v>79221</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3773,10 +3773,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>489169</v>
+        <v>489243</v>
       </c>
       <c r="R30" t="n">
-        <v>6720185</v>
+        <v>6719933</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3808,7 +3808,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3818,7 +3818,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4701,32 +4701,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130800608</v>
+        <v>130800707</v>
       </c>
       <c r="B39" t="n">
-        <v>92147</v>
+        <v>79221</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4736,10 +4736,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>489214</v>
+        <v>489119</v>
       </c>
       <c r="R39" t="n">
-        <v>6719996</v>
+        <v>6720040</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4771,7 +4771,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4808,7 +4808,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130800714</v>
+        <v>130800677</v>
       </c>
       <c r="B40" t="n">
         <v>79221</v>
@@ -4843,10 +4843,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>489163</v>
+        <v>489132</v>
       </c>
       <c r="R40" t="n">
-        <v>6720122</v>
+        <v>6720123</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4878,7 +4878,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4915,32 +4915,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130800707</v>
+        <v>130800608</v>
       </c>
       <c r="B41" t="n">
-        <v>79221</v>
+        <v>92147</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4950,10 +4950,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>489119</v>
+        <v>489214</v>
       </c>
       <c r="R41" t="n">
-        <v>6720040</v>
+        <v>6719996</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4985,7 +4985,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4995,7 +4995,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5022,7 +5022,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130800677</v>
+        <v>130800714</v>
       </c>
       <c r="B42" t="n">
         <v>79221</v>
@@ -5057,10 +5057,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>489132</v>
+        <v>489163</v>
       </c>
       <c r="R42" t="n">
-        <v>6720123</v>
+        <v>6720122</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5092,7 +5092,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5102,7 +5102,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5236,7 +5236,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130800684</v>
+        <v>130800709</v>
       </c>
       <c r="B44" t="n">
         <v>79221</v>
@@ -5271,10 +5271,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>489177</v>
+        <v>489094</v>
       </c>
       <c r="R44" t="n">
-        <v>6720066</v>
+        <v>6720086</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5343,7 +5343,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130800709</v>
+        <v>130800684</v>
       </c>
       <c r="B45" t="n">
         <v>79221</v>
@@ -5378,10 +5378,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>489094</v>
+        <v>489177</v>
       </c>
       <c r="R45" t="n">
-        <v>6720086</v>
+        <v>6720066</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5423,7 +5423,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6750,10 +6750,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130800768</v>
+        <v>130800604</v>
       </c>
       <c r="B58" t="n">
-        <v>5177</v>
+        <v>5197</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6761,27 +6761,27 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -6790,10 +6790,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>489234</v>
+        <v>489244</v>
       </c>
       <c r="R58" t="n">
-        <v>6719934</v>
+        <v>6719935</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6835,7 +6835,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6862,50 +6862,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130800604</v>
+        <v>130800691</v>
       </c>
       <c r="B59" t="n">
-        <v>5197</v>
+        <v>79221</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>489244</v>
+        <v>489214</v>
       </c>
       <c r="R59" t="n">
-        <v>6719935</v>
+        <v>6720016</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6937,7 +6932,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6947,7 +6942,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6974,7 +6969,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130800691</v>
+        <v>130800702</v>
       </c>
       <c r="B60" t="n">
         <v>79221</v>
@@ -7009,10 +7004,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>489214</v>
+        <v>489258</v>
       </c>
       <c r="R60" t="n">
-        <v>6720016</v>
+        <v>6719949</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7044,7 +7039,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7054,7 +7049,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7081,7 +7076,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130800702</v>
+        <v>130800708</v>
       </c>
       <c r="B61" t="n">
         <v>79221</v>
@@ -7116,10 +7111,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>489258</v>
+        <v>489077</v>
       </c>
       <c r="R61" t="n">
-        <v>6719949</v>
+        <v>6720065</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7151,7 +7146,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7161,7 +7156,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7188,7 +7183,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130800708</v>
+        <v>130800705</v>
       </c>
       <c r="B62" t="n">
         <v>79221</v>
@@ -7223,10 +7218,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>489077</v>
+        <v>489144</v>
       </c>
       <c r="R62" t="n">
-        <v>6720065</v>
+        <v>6719996</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7258,7 +7253,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7268,7 +7263,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7295,45 +7290,50 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130800705</v>
+        <v>130800768</v>
       </c>
       <c r="B63" t="n">
-        <v>79221</v>
+        <v>5177</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>489144</v>
+        <v>489234</v>
       </c>
       <c r="R63" t="n">
-        <v>6719996</v>
+        <v>6719934</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7365,7 +7365,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7375,7 +7375,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7616,7 +7616,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130800694</v>
+        <v>130800692</v>
       </c>
       <c r="B66" t="n">
         <v>79221</v>
@@ -7651,10 +7651,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>489214</v>
+        <v>489211</v>
       </c>
       <c r="R66" t="n">
-        <v>6719991</v>
+        <v>6720011</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7686,7 +7686,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7696,7 +7696,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7723,7 +7723,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130800692</v>
+        <v>130800694</v>
       </c>
       <c r="B67" t="n">
         <v>79221</v>
@@ -7758,10 +7758,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>489211</v>
+        <v>489214</v>
       </c>
       <c r="R67" t="n">
-        <v>6720011</v>
+        <v>6719991</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7793,7 +7793,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7803,7 +7803,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7830,10 +7830,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130800711</v>
+        <v>130800620</v>
       </c>
       <c r="B68" t="n">
-        <v>79221</v>
+        <v>57861</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7841,34 +7841,39 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>489138</v>
+        <v>489144</v>
       </c>
       <c r="R68" t="n">
-        <v>6720109</v>
+        <v>6720087</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7900,7 +7905,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7910,7 +7915,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7937,10 +7942,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130800620</v>
+        <v>130800711</v>
       </c>
       <c r="B69" t="n">
-        <v>57861</v>
+        <v>79221</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7948,39 +7953,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>489144</v>
+        <v>489138</v>
       </c>
       <c r="R69" t="n">
-        <v>6720087</v>
+        <v>6720109</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8012,7 +8012,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8022,7 +8022,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD69" t="b">

--- a/artfynd/A 62861-2025 artfynd.xlsx
+++ b/artfynd/A 62861-2025 artfynd.xlsx
@@ -1892,7 +1892,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130800622</v>
+        <v>130800627</v>
       </c>
       <c r="B13" t="n">
         <v>57861</v>
@@ -1923,7 +1923,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1932,10 +1932,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>489171</v>
+        <v>489163</v>
       </c>
       <c r="R13" t="n">
-        <v>6720048</v>
+        <v>6719987</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1967,7 +1967,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1977,7 +1977,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2004,7 +2004,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130800627</v>
+        <v>130800622</v>
       </c>
       <c r="B14" t="n">
         <v>57861</v>
@@ -2035,7 +2035,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2044,10 +2044,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>489163</v>
+        <v>489171</v>
       </c>
       <c r="R14" t="n">
-        <v>6719987</v>
+        <v>6720048</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2079,7 +2079,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2116,7 +2116,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130800641</v>
+        <v>130800634</v>
       </c>
       <c r="B15" t="n">
         <v>8451</v>
@@ -2156,10 +2156,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>489210</v>
+        <v>489196</v>
       </c>
       <c r="R15" t="n">
-        <v>6720036</v>
+        <v>6720103</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2191,7 +2191,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2229,7 +2229,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130800634</v>
+        <v>130800641</v>
       </c>
       <c r="B16" t="n">
         <v>8451</v>
@@ -2269,10 +2269,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>489196</v>
+        <v>489210</v>
       </c>
       <c r="R16" t="n">
-        <v>6720103</v>
+        <v>6720036</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2314,7 +2314,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2342,10 +2342,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130800609</v>
+        <v>130800671</v>
       </c>
       <c r="B17" t="n">
-        <v>91776</v>
+        <v>79221</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2353,21 +2353,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>489172</v>
+        <v>489159</v>
       </c>
       <c r="R17" t="n">
-        <v>6720186</v>
+        <v>6720170</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2412,7 +2412,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2422,7 +2422,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2449,7 +2449,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130800671</v>
+        <v>130800689</v>
       </c>
       <c r="B18" t="n">
         <v>79221</v>
@@ -2484,10 +2484,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>489159</v>
+        <v>489171</v>
       </c>
       <c r="R18" t="n">
-        <v>6720170</v>
+        <v>6720037</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2519,7 +2519,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2529,7 +2529,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2556,10 +2556,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130800689</v>
+        <v>130800609</v>
       </c>
       <c r="B19" t="n">
-        <v>79221</v>
+        <v>91784</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2567,21 +2567,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>489171</v>
+        <v>489172</v>
       </c>
       <c r="R19" t="n">
-        <v>6720037</v>
+        <v>6720186</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2626,7 +2626,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2636,7 +2636,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2663,10 +2663,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130800621</v>
+        <v>130800710</v>
       </c>
       <c r="B20" t="n">
-        <v>57861</v>
+        <v>79221</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2674,39 +2674,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>489175</v>
+        <v>489124</v>
       </c>
       <c r="R20" t="n">
-        <v>6720065</v>
+        <v>6720109</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2738,7 +2733,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2748,7 +2743,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2775,7 +2770,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130800710</v>
+        <v>130800668</v>
       </c>
       <c r="B21" t="n">
         <v>79221</v>
@@ -2810,10 +2805,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>489124</v>
+        <v>489197</v>
       </c>
       <c r="R21" t="n">
-        <v>6720109</v>
+        <v>6720167</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2845,7 +2840,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2855,7 +2850,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2882,10 +2877,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130800668</v>
+        <v>130800621</v>
       </c>
       <c r="B22" t="n">
-        <v>79221</v>
+        <v>57861</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2893,34 +2888,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>489197</v>
+        <v>489175</v>
       </c>
       <c r="R22" t="n">
-        <v>6720167</v>
+        <v>6720065</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2952,7 +2952,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3310,7 +3310,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130800695</v>
+        <v>130800725</v>
       </c>
       <c r="B26" t="n">
         <v>79221</v>
@@ -3345,10 +3345,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>489231</v>
+        <v>489332</v>
       </c>
       <c r="R26" t="n">
-        <v>6719941</v>
+        <v>6720052</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3380,7 +3380,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3390,7 +3390,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3417,32 +3417,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130800606</v>
+        <v>130800696</v>
       </c>
       <c r="B27" t="n">
-        <v>92147</v>
+        <v>79221</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3452,10 +3452,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>489169</v>
+        <v>489243</v>
       </c>
       <c r="R27" t="n">
-        <v>6720185</v>
+        <v>6719933</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3487,7 +3487,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3524,7 +3524,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130800687</v>
+        <v>130800695</v>
       </c>
       <c r="B28" t="n">
         <v>79221</v>
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>489175</v>
+        <v>489231</v>
       </c>
       <c r="R28" t="n">
-        <v>6720053</v>
+        <v>6719941</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3594,7 +3594,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3604,7 +3604,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3631,7 +3631,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130800725</v>
+        <v>130800687</v>
       </c>
       <c r="B29" t="n">
         <v>79221</v>
@@ -3666,10 +3666,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>489332</v>
+        <v>489175</v>
       </c>
       <c r="R29" t="n">
-        <v>6720052</v>
+        <v>6720053</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3701,7 +3701,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3738,32 +3738,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130800696</v>
+        <v>130800606</v>
       </c>
       <c r="B30" t="n">
-        <v>79221</v>
+        <v>92155</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3773,10 +3773,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>489243</v>
+        <v>489169</v>
       </c>
       <c r="R30" t="n">
-        <v>6719933</v>
+        <v>6720185</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3808,7 +3808,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3818,7 +3818,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3845,7 +3845,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130800688</v>
+        <v>130800678</v>
       </c>
       <c r="B31" t="n">
         <v>79221</v>
@@ -3880,10 +3880,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>489168</v>
+        <v>489131</v>
       </c>
       <c r="R31" t="n">
-        <v>6720046</v>
+        <v>6720117</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3915,7 +3915,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3925,7 +3925,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3952,7 +3952,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130800678</v>
+        <v>130800688</v>
       </c>
       <c r="B32" t="n">
         <v>79221</v>
@@ -3987,10 +3987,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>489131</v>
+        <v>489168</v>
       </c>
       <c r="R32" t="n">
-        <v>6720117</v>
+        <v>6720046</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4032,7 +4032,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4380,7 +4380,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130800679</v>
+        <v>130800666</v>
       </c>
       <c r="B36" t="n">
         <v>79221</v>
@@ -4415,10 +4415,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>489122</v>
+        <v>489208</v>
       </c>
       <c r="R36" t="n">
-        <v>6720120</v>
+        <v>6720174</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4450,7 +4450,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4460,7 +4460,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4487,7 +4487,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130800676</v>
+        <v>130800679</v>
       </c>
       <c r="B37" t="n">
         <v>79221</v>
@@ -4522,10 +4522,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>489151</v>
+        <v>489122</v>
       </c>
       <c r="R37" t="n">
-        <v>6720144</v>
+        <v>6720120</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4557,7 +4557,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4567,7 +4567,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4594,7 +4594,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130800666</v>
+        <v>130800676</v>
       </c>
       <c r="B38" t="n">
         <v>79221</v>
@@ -4629,10 +4629,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>489208</v>
+        <v>489151</v>
       </c>
       <c r="R38" t="n">
-        <v>6720174</v>
+        <v>6720144</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4664,7 +4664,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4674,7 +4674,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4701,32 +4701,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130800707</v>
+        <v>130800608</v>
       </c>
       <c r="B39" t="n">
-        <v>79221</v>
+        <v>92155</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4736,10 +4736,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>489119</v>
+        <v>489214</v>
       </c>
       <c r="R39" t="n">
-        <v>6720040</v>
+        <v>6719996</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4771,7 +4771,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4808,7 +4808,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130800677</v>
+        <v>130800714</v>
       </c>
       <c r="B40" t="n">
         <v>79221</v>
@@ -4843,10 +4843,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>489132</v>
+        <v>489163</v>
       </c>
       <c r="R40" t="n">
-        <v>6720123</v>
+        <v>6720122</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4878,7 +4878,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4915,32 +4915,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130800608</v>
+        <v>130800707</v>
       </c>
       <c r="B41" t="n">
-        <v>92147</v>
+        <v>79221</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4950,10 +4950,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>489214</v>
+        <v>489119</v>
       </c>
       <c r="R41" t="n">
-        <v>6719996</v>
+        <v>6720040</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4985,7 +4985,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4995,7 +4995,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5022,7 +5022,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130800714</v>
+        <v>130800677</v>
       </c>
       <c r="B42" t="n">
         <v>79221</v>
@@ -5057,10 +5057,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>489163</v>
+        <v>489132</v>
       </c>
       <c r="R42" t="n">
-        <v>6720122</v>
+        <v>6720123</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5092,7 +5092,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5102,7 +5102,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5881,7 +5881,7 @@
         <v>130800610</v>
       </c>
       <c r="B50" t="n">
-        <v>91776</v>
+        <v>91784</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6638,27 +6638,27 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130800619</v>
+        <v>130800604</v>
       </c>
       <c r="B57" t="n">
-        <v>57861</v>
+        <v>5197</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -6669,7 +6669,7 @@
       <c r="I57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>489184</v>
+        <v>489244</v>
       </c>
       <c r="R57" t="n">
-        <v>6720170</v>
+        <v>6719935</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6713,7 +6713,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6723,7 +6723,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6750,50 +6750,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130800604</v>
+        <v>130800691</v>
       </c>
       <c r="B58" t="n">
-        <v>5197</v>
+        <v>79221</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>489244</v>
+        <v>489214</v>
       </c>
       <c r="R58" t="n">
-        <v>6719935</v>
+        <v>6720016</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6825,7 +6820,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6835,7 +6830,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6862,7 +6857,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130800691</v>
+        <v>130800705</v>
       </c>
       <c r="B59" t="n">
         <v>79221</v>
@@ -6897,10 +6892,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>489214</v>
+        <v>489144</v>
       </c>
       <c r="R59" t="n">
-        <v>6720016</v>
+        <v>6719996</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6932,7 +6927,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6942,7 +6937,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7183,10 +7178,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130800705</v>
+        <v>130800619</v>
       </c>
       <c r="B62" t="n">
-        <v>79221</v>
+        <v>57861</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7194,34 +7189,39 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>489144</v>
+        <v>489184</v>
       </c>
       <c r="R62" t="n">
-        <v>6719996</v>
+        <v>6720170</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7253,7 +7253,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7263,7 +7263,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7402,7 +7402,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130800674</v>
+        <v>130800665</v>
       </c>
       <c r="B64" t="n">
         <v>79221</v>
@@ -7437,10 +7437,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>489168</v>
+        <v>489208</v>
       </c>
       <c r="R64" t="n">
-        <v>6720197</v>
+        <v>6720188</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7472,7 +7472,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7482,7 +7482,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7509,7 +7509,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130800665</v>
+        <v>130800692</v>
       </c>
       <c r="B65" t="n">
         <v>79221</v>
@@ -7544,10 +7544,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>489208</v>
+        <v>489211</v>
       </c>
       <c r="R65" t="n">
-        <v>6720188</v>
+        <v>6720011</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7579,7 +7579,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7589,7 +7589,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7616,7 +7616,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130800692</v>
+        <v>130800674</v>
       </c>
       <c r="B66" t="n">
         <v>79221</v>
@@ -7651,10 +7651,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>489211</v>
+        <v>489168</v>
       </c>
       <c r="R66" t="n">
-        <v>6720011</v>
+        <v>6720197</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7686,7 +7686,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7696,7 +7696,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7830,10 +7830,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130800620</v>
+        <v>130800711</v>
       </c>
       <c r="B68" t="n">
-        <v>57861</v>
+        <v>79221</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7841,39 +7841,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>489144</v>
+        <v>489138</v>
       </c>
       <c r="R68" t="n">
-        <v>6720087</v>
+        <v>6720109</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7905,7 +7900,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7915,7 +7910,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7942,10 +7937,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130800711</v>
+        <v>130800620</v>
       </c>
       <c r="B69" t="n">
-        <v>79221</v>
+        <v>57861</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7953,34 +7948,39 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>489138</v>
+        <v>489144</v>
       </c>
       <c r="R69" t="n">
-        <v>6720109</v>
+        <v>6720087</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8012,7 +8012,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8022,7 +8022,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD69" t="b">

--- a/artfynd/A 62861-2025 artfynd.xlsx
+++ b/artfynd/A 62861-2025 artfynd.xlsx
@@ -2116,7 +2116,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130800634</v>
+        <v>130800641</v>
       </c>
       <c r="B15" t="n">
         <v>8451</v>
@@ -2156,10 +2156,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>489196</v>
+        <v>489210</v>
       </c>
       <c r="R15" t="n">
-        <v>6720103</v>
+        <v>6720036</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2191,7 +2191,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2229,7 +2229,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130800641</v>
+        <v>130800634</v>
       </c>
       <c r="B16" t="n">
         <v>8451</v>
@@ -2269,10 +2269,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>489210</v>
+        <v>489196</v>
       </c>
       <c r="R16" t="n">
-        <v>6720036</v>
+        <v>6720103</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2314,7 +2314,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2342,10 +2342,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130800671</v>
+        <v>130800609</v>
       </c>
       <c r="B17" t="n">
-        <v>79221</v>
+        <v>91784</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2353,21 +2353,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>489159</v>
+        <v>489172</v>
       </c>
       <c r="R17" t="n">
-        <v>6720170</v>
+        <v>6720186</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2412,7 +2412,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2422,7 +2422,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2449,7 +2449,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130800689</v>
+        <v>130800671</v>
       </c>
       <c r="B18" t="n">
         <v>79221</v>
@@ -2484,10 +2484,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>489171</v>
+        <v>489159</v>
       </c>
       <c r="R18" t="n">
-        <v>6720037</v>
+        <v>6720170</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2519,7 +2519,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2529,7 +2529,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2556,10 +2556,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130800609</v>
+        <v>130800689</v>
       </c>
       <c r="B19" t="n">
-        <v>91784</v>
+        <v>79221</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2567,21 +2567,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>489172</v>
+        <v>489171</v>
       </c>
       <c r="R19" t="n">
-        <v>6720186</v>
+        <v>6720037</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2626,7 +2626,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2636,7 +2636,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3310,32 +3310,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130800725</v>
+        <v>130800606</v>
       </c>
       <c r="B26" t="n">
-        <v>79221</v>
+        <v>92155</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3345,10 +3345,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>489332</v>
+        <v>489169</v>
       </c>
       <c r="R26" t="n">
-        <v>6720052</v>
+        <v>6720185</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3380,7 +3380,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3390,7 +3390,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3417,7 +3417,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130800696</v>
+        <v>130800695</v>
       </c>
       <c r="B27" t="n">
         <v>79221</v>
@@ -3452,10 +3452,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>489243</v>
+        <v>489231</v>
       </c>
       <c r="R27" t="n">
-        <v>6719933</v>
+        <v>6719941</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3487,7 +3487,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3524,7 +3524,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130800695</v>
+        <v>130800687</v>
       </c>
       <c r="B28" t="n">
         <v>79221</v>
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>489231</v>
+        <v>489175</v>
       </c>
       <c r="R28" t="n">
-        <v>6719941</v>
+        <v>6720053</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3594,7 +3594,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3604,7 +3604,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3631,7 +3631,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130800687</v>
+        <v>130800725</v>
       </c>
       <c r="B29" t="n">
         <v>79221</v>
@@ -3666,10 +3666,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>489175</v>
+        <v>489332</v>
       </c>
       <c r="R29" t="n">
-        <v>6720053</v>
+        <v>6720052</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3701,7 +3701,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3738,32 +3738,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130800606</v>
+        <v>130800696</v>
       </c>
       <c r="B30" t="n">
-        <v>92155</v>
+        <v>79221</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3773,10 +3773,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>489169</v>
+        <v>489243</v>
       </c>
       <c r="R30" t="n">
-        <v>6720185</v>
+        <v>6719933</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3808,7 +3808,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3818,7 +3818,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3952,7 +3952,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130800688</v>
+        <v>130800716</v>
       </c>
       <c r="B32" t="n">
         <v>79221</v>
@@ -3987,10 +3987,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>489168</v>
+        <v>489172</v>
       </c>
       <c r="R32" t="n">
-        <v>6720046</v>
+        <v>6720145</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4032,7 +4032,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4059,7 +4059,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130800716</v>
+        <v>130800688</v>
       </c>
       <c r="B33" t="n">
         <v>79221</v>
@@ -4094,10 +4094,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>489172</v>
+        <v>489168</v>
       </c>
       <c r="R33" t="n">
-        <v>6720145</v>
+        <v>6720046</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4139,7 +4139,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4380,7 +4380,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130800666</v>
+        <v>130800679</v>
       </c>
       <c r="B36" t="n">
         <v>79221</v>
@@ -4415,10 +4415,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>489208</v>
+        <v>489122</v>
       </c>
       <c r="R36" t="n">
-        <v>6720174</v>
+        <v>6720120</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4450,7 +4450,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4460,7 +4460,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4487,7 +4487,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130800679</v>
+        <v>130800676</v>
       </c>
       <c r="B37" t="n">
         <v>79221</v>
@@ -4522,10 +4522,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>489122</v>
+        <v>489151</v>
       </c>
       <c r="R37" t="n">
-        <v>6720120</v>
+        <v>6720144</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4557,7 +4557,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4567,7 +4567,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4594,7 +4594,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130800676</v>
+        <v>130800666</v>
       </c>
       <c r="B38" t="n">
         <v>79221</v>
@@ -4629,10 +4629,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>489151</v>
+        <v>489208</v>
       </c>
       <c r="R38" t="n">
-        <v>6720144</v>
+        <v>6720174</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4664,7 +4664,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4674,7 +4674,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5129,7 +5129,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130800681</v>
+        <v>130800684</v>
       </c>
       <c r="B43" t="n">
         <v>79221</v>
@@ -5164,10 +5164,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>489138</v>
+        <v>489177</v>
       </c>
       <c r="R43" t="n">
-        <v>6720092</v>
+        <v>6720066</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5199,7 +5199,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5209,7 +5209,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5236,7 +5236,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130800709</v>
+        <v>130800681</v>
       </c>
       <c r="B44" t="n">
         <v>79221</v>
@@ -5271,10 +5271,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>489094</v>
+        <v>489138</v>
       </c>
       <c r="R44" t="n">
-        <v>6720086</v>
+        <v>6720092</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5343,7 +5343,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130800684</v>
+        <v>130800709</v>
       </c>
       <c r="B45" t="n">
         <v>79221</v>
@@ -5378,10 +5378,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>489177</v>
+        <v>489094</v>
       </c>
       <c r="R45" t="n">
-        <v>6720066</v>
+        <v>6720086</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5423,7 +5423,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5664,10 +5664,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130800704</v>
+        <v>130800610</v>
       </c>
       <c r="B48" t="n">
-        <v>79221</v>
+        <v>91784</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5675,21 +5675,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5699,10 +5699,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>489180</v>
+        <v>489216</v>
       </c>
       <c r="R48" t="n">
-        <v>6719972</v>
+        <v>6719995</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5734,7 +5734,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5744,7 +5744,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5771,7 +5771,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130800715</v>
+        <v>130800704</v>
       </c>
       <c r="B49" t="n">
         <v>79221</v>
@@ -5806,10 +5806,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>489166</v>
+        <v>489180</v>
       </c>
       <c r="R49" t="n">
-        <v>6720127</v>
+        <v>6719972</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5841,7 +5841,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5878,10 +5878,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130800610</v>
+        <v>130800715</v>
       </c>
       <c r="B50" t="n">
-        <v>91784</v>
+        <v>79221</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5889,21 +5889,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5913,10 +5913,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>489216</v>
+        <v>489166</v>
       </c>
       <c r="R50" t="n">
-        <v>6719995</v>
+        <v>6720127</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5948,7 +5948,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6638,50 +6638,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130800604</v>
+        <v>130800702</v>
       </c>
       <c r="B57" t="n">
-        <v>5197</v>
+        <v>79221</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>489244</v>
+        <v>489258</v>
       </c>
       <c r="R57" t="n">
-        <v>6719935</v>
+        <v>6719949</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6713,7 +6708,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6723,7 +6718,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6750,10 +6745,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130800691</v>
+        <v>130800619</v>
       </c>
       <c r="B58" t="n">
-        <v>79221</v>
+        <v>57861</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6761,34 +6756,39 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>489214</v>
+        <v>489184</v>
       </c>
       <c r="R58" t="n">
-        <v>6720016</v>
+        <v>6720170</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6820,7 +6820,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6830,7 +6830,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6857,45 +6857,50 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130800705</v>
+        <v>130800604</v>
       </c>
       <c r="B59" t="n">
-        <v>79221</v>
+        <v>5197</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>105930</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>489144</v>
+        <v>489244</v>
       </c>
       <c r="R59" t="n">
-        <v>6719996</v>
+        <v>6719935</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6927,7 +6932,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6937,7 +6942,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6964,7 +6969,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130800702</v>
+        <v>130800691</v>
       </c>
       <c r="B60" t="n">
         <v>79221</v>
@@ -6999,10 +7004,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>489258</v>
+        <v>489214</v>
       </c>
       <c r="R60" t="n">
-        <v>6719949</v>
+        <v>6720016</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7034,7 +7039,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7044,7 +7049,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7178,10 +7183,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130800619</v>
+        <v>130800705</v>
       </c>
       <c r="B62" t="n">
-        <v>57861</v>
+        <v>79221</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7189,39 +7194,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>489184</v>
+        <v>489144</v>
       </c>
       <c r="R62" t="n">
-        <v>6720170</v>
+        <v>6719996</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7253,7 +7253,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7263,7 +7263,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7402,7 +7402,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130800665</v>
+        <v>130800674</v>
       </c>
       <c r="B64" t="n">
         <v>79221</v>
@@ -7437,10 +7437,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>489208</v>
+        <v>489168</v>
       </c>
       <c r="R64" t="n">
-        <v>6720188</v>
+        <v>6720197</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7472,7 +7472,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7482,7 +7482,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7509,7 +7509,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130800692</v>
+        <v>130800665</v>
       </c>
       <c r="B65" t="n">
         <v>79221</v>
@@ -7544,10 +7544,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>489211</v>
+        <v>489208</v>
       </c>
       <c r="R65" t="n">
-        <v>6720011</v>
+        <v>6720188</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7579,7 +7579,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7589,7 +7589,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7616,7 +7616,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130800674</v>
+        <v>130800694</v>
       </c>
       <c r="B66" t="n">
         <v>79221</v>
@@ -7651,10 +7651,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>489168</v>
+        <v>489214</v>
       </c>
       <c r="R66" t="n">
-        <v>6720197</v>
+        <v>6719991</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7686,7 +7686,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7696,7 +7696,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7723,7 +7723,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130800694</v>
+        <v>130800692</v>
       </c>
       <c r="B67" t="n">
         <v>79221</v>
@@ -7758,10 +7758,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>489214</v>
+        <v>489211</v>
       </c>
       <c r="R67" t="n">
-        <v>6719991</v>
+        <v>6720011</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7793,7 +7793,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7803,7 +7803,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD67" t="b">

--- a/artfynd/A 62861-2025 artfynd.xlsx
+++ b/artfynd/A 62861-2025 artfynd.xlsx
@@ -1250,7 +1250,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130800726</v>
+        <v>130800713</v>
       </c>
       <c r="B7" t="n">
         <v>79243</v>
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>489323</v>
+        <v>489149</v>
       </c>
       <c r="R7" t="n">
-        <v>6720025</v>
+        <v>6720123</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,7 +1357,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130800713</v>
+        <v>130800726</v>
       </c>
       <c r="B8" t="n">
         <v>79243</v>
@@ -1392,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>489149</v>
+        <v>489323</v>
       </c>
       <c r="R8" t="n">
-        <v>6720123</v>
+        <v>6720025</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1571,7 +1571,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130800672</v>
+        <v>130800721</v>
       </c>
       <c r="B10" t="n">
         <v>79243</v>
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>489170</v>
+        <v>489189</v>
       </c>
       <c r="R10" t="n">
-        <v>6720188</v>
+        <v>6720073</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2009,7 +2009,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130800721</v>
+        <v>130800672</v>
       </c>
       <c r="B14" t="n">
         <v>79243</v>
@@ -2044,10 +2044,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>489189</v>
+        <v>489170</v>
       </c>
       <c r="R14" t="n">
-        <v>6720073</v>
+        <v>6720188</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2079,7 +2079,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2663,7 +2663,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130800710</v>
+        <v>130800668</v>
       </c>
       <c r="B20" t="n">
         <v>79243</v>
@@ -2698,10 +2698,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>489124</v>
+        <v>489197</v>
       </c>
       <c r="R20" t="n">
-        <v>6720109</v>
+        <v>6720167</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2733,7 +2733,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2743,7 +2743,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2770,10 +2770,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130800668</v>
+        <v>130800621</v>
       </c>
       <c r="B21" t="n">
-        <v>79243</v>
+        <v>57881</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2781,34 +2781,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>489197</v>
+        <v>489175</v>
       </c>
       <c r="R21" t="n">
-        <v>6720167</v>
+        <v>6720065</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2840,7 +2845,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2850,7 +2855,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2877,10 +2882,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130800621</v>
+        <v>130800710</v>
       </c>
       <c r="B22" t="n">
-        <v>57881</v>
+        <v>79243</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2888,39 +2893,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>489175</v>
+        <v>489124</v>
       </c>
       <c r="R22" t="n">
-        <v>6720065</v>
+        <v>6720109</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2952,7 +2952,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2989,7 +2989,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130800690</v>
+        <v>130800682</v>
       </c>
       <c r="B23" t="n">
         <v>79243</v>
@@ -3024,10 +3024,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>489198</v>
+        <v>489151</v>
       </c>
       <c r="R23" t="n">
-        <v>6720010</v>
+        <v>6720086</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3096,7 +3096,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130800718</v>
+        <v>130800690</v>
       </c>
       <c r="B24" t="n">
         <v>79243</v>
@@ -3131,10 +3131,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>489189</v>
+        <v>489198</v>
       </c>
       <c r="R24" t="n">
-        <v>6720114</v>
+        <v>6720010</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3166,7 +3166,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3203,7 +3203,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130800682</v>
+        <v>130800718</v>
       </c>
       <c r="B25" t="n">
         <v>79243</v>
@@ -3238,10 +3238,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>489151</v>
+        <v>489189</v>
       </c>
       <c r="R25" t="n">
-        <v>6720086</v>
+        <v>6720114</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3273,7 +3273,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3417,7 +3417,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130800725</v>
+        <v>130800696</v>
       </c>
       <c r="B27" t="n">
         <v>79243</v>
@@ -3452,10 +3452,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>489332</v>
+        <v>489243</v>
       </c>
       <c r="R27" t="n">
-        <v>6720052</v>
+        <v>6719933</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3487,7 +3487,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3738,7 +3738,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130800696</v>
+        <v>130800725</v>
       </c>
       <c r="B30" t="n">
         <v>79243</v>
@@ -3773,10 +3773,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>489243</v>
+        <v>489332</v>
       </c>
       <c r="R30" t="n">
-        <v>6719933</v>
+        <v>6720052</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3808,7 +3808,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3818,7 +3818,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3845,7 +3845,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130800688</v>
+        <v>130800678</v>
       </c>
       <c r="B31" t="n">
         <v>79243</v>
@@ -3880,10 +3880,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>489168</v>
+        <v>489131</v>
       </c>
       <c r="R31" t="n">
-        <v>6720046</v>
+        <v>6720117</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3915,7 +3915,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3925,7 +3925,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3952,7 +3952,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130800678</v>
+        <v>130800716</v>
       </c>
       <c r="B32" t="n">
         <v>79243</v>
@@ -3987,10 +3987,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>489131</v>
+        <v>489172</v>
       </c>
       <c r="R32" t="n">
-        <v>6720117</v>
+        <v>6720145</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4032,7 +4032,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4059,7 +4059,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130800716</v>
+        <v>130800688</v>
       </c>
       <c r="B33" t="n">
         <v>79243</v>
@@ -4094,10 +4094,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>489172</v>
+        <v>489168</v>
       </c>
       <c r="R33" t="n">
-        <v>6720145</v>
+        <v>6720046</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4139,7 +4139,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4166,7 +4166,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130800712</v>
+        <v>130800669</v>
       </c>
       <c r="B34" t="n">
         <v>79243</v>
@@ -4201,10 +4201,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>489143</v>
+        <v>489170</v>
       </c>
       <c r="R34" t="n">
-        <v>6720114</v>
+        <v>6720167</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4236,7 +4236,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4246,7 +4246,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4273,7 +4273,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130800669</v>
+        <v>130800712</v>
       </c>
       <c r="B35" t="n">
         <v>79243</v>
@@ -4308,10 +4308,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>489170</v>
+        <v>489143</v>
       </c>
       <c r="R35" t="n">
-        <v>6720167</v>
+        <v>6720114</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4343,7 +4343,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4353,7 +4353,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4380,7 +4380,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130800676</v>
+        <v>130800679</v>
       </c>
       <c r="B36" t="n">
         <v>79243</v>
@@ -4415,10 +4415,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>489151</v>
+        <v>489122</v>
       </c>
       <c r="R36" t="n">
-        <v>6720144</v>
+        <v>6720120</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4450,7 +4450,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4460,7 +4460,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4487,7 +4487,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130800666</v>
+        <v>130800676</v>
       </c>
       <c r="B37" t="n">
         <v>79243</v>
@@ -4522,10 +4522,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>489208</v>
+        <v>489151</v>
       </c>
       <c r="R37" t="n">
-        <v>6720174</v>
+        <v>6720144</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4557,7 +4557,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4567,7 +4567,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4594,7 +4594,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130800679</v>
+        <v>130800666</v>
       </c>
       <c r="B38" t="n">
         <v>79243</v>
@@ -4629,10 +4629,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>489122</v>
+        <v>489208</v>
       </c>
       <c r="R38" t="n">
-        <v>6720120</v>
+        <v>6720174</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4664,7 +4664,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4674,7 +4674,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5236,7 +5236,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130800667</v>
+        <v>130800681</v>
       </c>
       <c r="B44" t="n">
         <v>79243</v>
@@ -5271,10 +5271,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>489199</v>
+        <v>489138</v>
       </c>
       <c r="R44" t="n">
-        <v>6720176</v>
+        <v>6720092</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5343,7 +5343,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130800681</v>
+        <v>130800684</v>
       </c>
       <c r="B45" t="n">
         <v>79243</v>
@@ -5378,10 +5378,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>489138</v>
+        <v>489177</v>
       </c>
       <c r="R45" t="n">
-        <v>6720092</v>
+        <v>6720066</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5423,7 +5423,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5450,7 +5450,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130800684</v>
+        <v>130800667</v>
       </c>
       <c r="B46" t="n">
         <v>79243</v>
@@ -5485,10 +5485,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>489177</v>
+        <v>489199</v>
       </c>
       <c r="R46" t="n">
-        <v>6720066</v>
+        <v>6720176</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5520,7 +5520,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5530,7 +5530,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5664,10 +5664,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130800704</v>
+        <v>130800610</v>
       </c>
       <c r="B48" t="n">
-        <v>79243</v>
+        <v>91808</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5675,21 +5675,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5699,10 +5699,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>489180</v>
+        <v>489216</v>
       </c>
       <c r="R48" t="n">
-        <v>6719972</v>
+        <v>6719995</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5734,7 +5734,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5744,7 +5744,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5771,7 +5771,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130800715</v>
+        <v>130800704</v>
       </c>
       <c r="B49" t="n">
         <v>79243</v>
@@ -5806,10 +5806,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>489166</v>
+        <v>489180</v>
       </c>
       <c r="R49" t="n">
-        <v>6720127</v>
+        <v>6719972</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5841,7 +5841,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5878,10 +5878,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130800610</v>
+        <v>130800715</v>
       </c>
       <c r="B50" t="n">
-        <v>91808</v>
+        <v>79243</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5889,21 +5889,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5913,10 +5913,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>489216</v>
+        <v>489166</v>
       </c>
       <c r="R50" t="n">
-        <v>6719995</v>
+        <v>6720127</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5948,7 +5948,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5985,10 +5985,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130800673</v>
+        <v>130800630</v>
       </c>
       <c r="B51" t="n">
-        <v>79243</v>
+        <v>57881</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5996,34 +5996,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>489180</v>
+        <v>489207</v>
       </c>
       <c r="R51" t="n">
-        <v>6720180</v>
+        <v>6720041</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6055,7 +6060,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6065,7 +6070,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6092,10 +6097,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130800630</v>
+        <v>130800673</v>
       </c>
       <c r="B52" t="n">
-        <v>57881</v>
+        <v>79243</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6103,39 +6108,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>489207</v>
+        <v>489180</v>
       </c>
       <c r="R52" t="n">
-        <v>6720041</v>
+        <v>6720180</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6167,7 +6167,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6177,7 +6177,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6418,50 +6418,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130800637</v>
+        <v>130800683</v>
       </c>
       <c r="B55" t="n">
-        <v>8451</v>
+        <v>79243</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>489091</v>
+        <v>489169</v>
       </c>
       <c r="R55" t="n">
-        <v>6720083</v>
+        <v>6720075</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6493,7 +6488,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6503,7 +6498,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6512,7 +6507,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6531,45 +6525,50 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130800683</v>
+        <v>130800637</v>
       </c>
       <c r="B56" t="n">
-        <v>79243</v>
+        <v>8451</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>489169</v>
+        <v>489091</v>
       </c>
       <c r="R56" t="n">
-        <v>6720075</v>
+        <v>6720083</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6601,7 +6600,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6611,7 +6610,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6620,6 +6619,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6638,50 +6638,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130800604</v>
+        <v>130800691</v>
       </c>
       <c r="B57" t="n">
-        <v>5197</v>
+        <v>79243</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>489244</v>
+        <v>489214</v>
       </c>
       <c r="R57" t="n">
-        <v>6719935</v>
+        <v>6720016</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6713,7 +6708,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6723,7 +6718,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6750,45 +6745,50 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130800702</v>
+        <v>130800604</v>
       </c>
       <c r="B58" t="n">
-        <v>79243</v>
+        <v>5197</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>105930</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>489258</v>
+        <v>489244</v>
       </c>
       <c r="R58" t="n">
-        <v>6719949</v>
+        <v>6719935</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6820,7 +6820,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6830,7 +6830,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6857,7 +6857,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130800708</v>
+        <v>130800702</v>
       </c>
       <c r="B59" t="n">
         <v>79243</v>
@@ -6892,10 +6892,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>489077</v>
+        <v>489258</v>
       </c>
       <c r="R59" t="n">
-        <v>6720065</v>
+        <v>6719949</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6927,7 +6927,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6937,7 +6937,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7183,7 +7183,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130800691</v>
+        <v>130800708</v>
       </c>
       <c r="B62" t="n">
         <v>79243</v>
@@ -7218,10 +7218,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>489214</v>
+        <v>489077</v>
       </c>
       <c r="R62" t="n">
-        <v>6720016</v>
+        <v>6720065</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7253,7 +7253,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7263,7 +7263,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD62" t="b">

--- a/artfynd/A 62861-2025 artfynd.xlsx
+++ b/artfynd/A 62861-2025 artfynd.xlsx
@@ -2223,50 +2223,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130800641</v>
+        <v>130800689</v>
       </c>
       <c r="B16" t="n">
-        <v>8451</v>
+        <v>79243</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>489210</v>
+        <v>489171</v>
       </c>
       <c r="R16" t="n">
-        <v>6720036</v>
+        <v>6720037</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2298,7 +2293,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2308,7 +2303,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2317,7 +2312,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2336,50 +2330,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130800634</v>
+        <v>130800671</v>
       </c>
       <c r="B17" t="n">
-        <v>8451</v>
+        <v>79243</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>489196</v>
+        <v>489159</v>
       </c>
       <c r="R17" t="n">
-        <v>6720103</v>
+        <v>6720170</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2411,7 +2400,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2421,7 +2410,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2430,7 +2419,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2449,45 +2437,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130800671</v>
+        <v>130800641</v>
       </c>
       <c r="B18" t="n">
-        <v>79243</v>
+        <v>8451</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>489159</v>
+        <v>489210</v>
       </c>
       <c r="R18" t="n">
-        <v>6720170</v>
+        <v>6720036</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2519,7 +2512,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2529,7 +2522,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2538,6 +2531,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2556,45 +2550,50 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130800689</v>
+        <v>130800634</v>
       </c>
       <c r="B19" t="n">
-        <v>79243</v>
+        <v>8451</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>489171</v>
+        <v>489196</v>
       </c>
       <c r="R19" t="n">
-        <v>6720037</v>
+        <v>6720103</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2626,7 +2625,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2636,7 +2635,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2645,6 +2644,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2663,7 +2663,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130800668</v>
+        <v>130800710</v>
       </c>
       <c r="B20" t="n">
         <v>79243</v>
@@ -2698,10 +2698,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>489197</v>
+        <v>489124</v>
       </c>
       <c r="R20" t="n">
-        <v>6720167</v>
+        <v>6720109</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2733,7 +2733,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2743,7 +2743,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2770,10 +2770,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130800621</v>
+        <v>130800668</v>
       </c>
       <c r="B21" t="n">
-        <v>57881</v>
+        <v>79243</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2781,39 +2781,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>489175</v>
+        <v>489197</v>
       </c>
       <c r="R21" t="n">
-        <v>6720065</v>
+        <v>6720167</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2845,7 +2840,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2855,7 +2850,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2882,10 +2877,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130800710</v>
+        <v>130800621</v>
       </c>
       <c r="B22" t="n">
-        <v>79243</v>
+        <v>57881</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2893,34 +2888,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>489124</v>
+        <v>489175</v>
       </c>
       <c r="R22" t="n">
-        <v>6720109</v>
+        <v>6720065</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2952,7 +2952,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2989,7 +2989,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130800682</v>
+        <v>130800690</v>
       </c>
       <c r="B23" t="n">
         <v>79243</v>
@@ -3024,10 +3024,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>489151</v>
+        <v>489198</v>
       </c>
       <c r="R23" t="n">
-        <v>6720086</v>
+        <v>6720010</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3096,7 +3096,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130800690</v>
+        <v>130800718</v>
       </c>
       <c r="B24" t="n">
         <v>79243</v>
@@ -3131,10 +3131,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>489198</v>
+        <v>489189</v>
       </c>
       <c r="R24" t="n">
-        <v>6720010</v>
+        <v>6720114</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3166,7 +3166,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3203,7 +3203,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130800718</v>
+        <v>130800682</v>
       </c>
       <c r="B25" t="n">
         <v>79243</v>
@@ -3238,10 +3238,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>489189</v>
+        <v>489151</v>
       </c>
       <c r="R25" t="n">
-        <v>6720114</v>
+        <v>6720086</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3273,7 +3273,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3845,7 +3845,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130800678</v>
+        <v>130800688</v>
       </c>
       <c r="B31" t="n">
         <v>79243</v>
@@ -3880,10 +3880,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>489131</v>
+        <v>489168</v>
       </c>
       <c r="R31" t="n">
-        <v>6720117</v>
+        <v>6720046</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3915,7 +3915,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3925,7 +3925,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3952,7 +3952,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130800716</v>
+        <v>130800678</v>
       </c>
       <c r="B32" t="n">
         <v>79243</v>
@@ -3987,10 +3987,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>489172</v>
+        <v>489131</v>
       </c>
       <c r="R32" t="n">
-        <v>6720145</v>
+        <v>6720117</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4032,7 +4032,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4059,7 +4059,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130800688</v>
+        <v>130800716</v>
       </c>
       <c r="B33" t="n">
         <v>79243</v>
@@ -4094,10 +4094,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>489168</v>
+        <v>489172</v>
       </c>
       <c r="R33" t="n">
-        <v>6720046</v>
+        <v>6720145</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4139,7 +4139,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 62861-2025 artfynd.xlsx
+++ b/artfynd/A 62861-2025 artfynd.xlsx
@@ -1571,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130800721</v>
+        <v>130800627</v>
       </c>
       <c r="B10" t="n">
-        <v>79243</v>
+        <v>57881</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1582,34 +1582,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>489189</v>
+        <v>489163</v>
       </c>
       <c r="R10" t="n">
-        <v>6720073</v>
+        <v>6719987</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1641,7 +1646,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1651,7 +1656,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1678,7 +1683,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130800627</v>
+        <v>130800622</v>
       </c>
       <c r="B11" t="n">
         <v>57881</v>
@@ -1709,7 +1714,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1718,10 +1723,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>489163</v>
+        <v>489171</v>
       </c>
       <c r="R11" t="n">
-        <v>6719987</v>
+        <v>6720048</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1753,7 +1758,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1763,7 +1768,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1790,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130800622</v>
+        <v>130800706</v>
       </c>
       <c r="B12" t="n">
-        <v>57881</v>
+        <v>79243</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1801,39 +1806,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>489171</v>
+        <v>489143</v>
       </c>
       <c r="R12" t="n">
-        <v>6720048</v>
+        <v>6720009</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1865,7 +1865,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1902,7 +1902,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130800706</v>
+        <v>130800721</v>
       </c>
       <c r="B13" t="n">
         <v>79243</v>
@@ -1937,10 +1937,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>489143</v>
+        <v>489189</v>
       </c>
       <c r="R13" t="n">
-        <v>6720009</v>
+        <v>6720073</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1972,7 +1972,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2116,10 +2116,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130800609</v>
+        <v>130800689</v>
       </c>
       <c r="B15" t="n">
-        <v>91808</v>
+        <v>79243</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2127,21 +2127,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2151,10 +2151,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>489172</v>
+        <v>489171</v>
       </c>
       <c r="R15" t="n">
-        <v>6720186</v>
+        <v>6720037</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2223,45 +2223,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130800689</v>
+        <v>130800634</v>
       </c>
       <c r="B16" t="n">
-        <v>79243</v>
+        <v>8451</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>489171</v>
+        <v>489196</v>
       </c>
       <c r="R16" t="n">
-        <v>6720037</v>
+        <v>6720103</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2293,7 +2298,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2303,7 +2308,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2312,6 +2317,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2330,10 +2336,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130800671</v>
+        <v>130800609</v>
       </c>
       <c r="B17" t="n">
-        <v>79243</v>
+        <v>91808</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2341,21 +2347,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2365,10 +2371,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>489159</v>
+        <v>489172</v>
       </c>
       <c r="R17" t="n">
-        <v>6720170</v>
+        <v>6720186</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2400,7 +2406,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2410,7 +2416,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2437,50 +2443,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130800641</v>
+        <v>130800671</v>
       </c>
       <c r="B18" t="n">
-        <v>8451</v>
+        <v>79243</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>489210</v>
+        <v>489159</v>
       </c>
       <c r="R18" t="n">
-        <v>6720036</v>
+        <v>6720170</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2512,7 +2513,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2522,7 +2523,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2531,7 +2532,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2550,7 +2550,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130800634</v>
+        <v>130800641</v>
       </c>
       <c r="B19" t="n">
         <v>8451</v>
@@ -2590,10 +2590,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>489196</v>
+        <v>489210</v>
       </c>
       <c r="R19" t="n">
-        <v>6720103</v>
+        <v>6720036</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2625,7 +2625,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2635,7 +2635,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2663,10 +2663,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130800710</v>
+        <v>130800621</v>
       </c>
       <c r="B20" t="n">
-        <v>79243</v>
+        <v>57881</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2674,34 +2674,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>489124</v>
+        <v>489175</v>
       </c>
       <c r="R20" t="n">
-        <v>6720109</v>
+        <v>6720065</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2733,7 +2738,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2743,7 +2748,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2877,10 +2882,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130800621</v>
+        <v>130800710</v>
       </c>
       <c r="B22" t="n">
-        <v>57881</v>
+        <v>79243</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2888,39 +2893,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>489175</v>
+        <v>489124</v>
       </c>
       <c r="R22" t="n">
-        <v>6720065</v>
+        <v>6720109</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2952,7 +2952,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2989,7 +2989,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130800690</v>
+        <v>130800718</v>
       </c>
       <c r="B23" t="n">
         <v>79243</v>
@@ -3024,10 +3024,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>489198</v>
+        <v>489189</v>
       </c>
       <c r="R23" t="n">
-        <v>6720010</v>
+        <v>6720114</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3096,7 +3096,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130800718</v>
+        <v>130800682</v>
       </c>
       <c r="B24" t="n">
         <v>79243</v>
@@ -3131,10 +3131,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>489189</v>
+        <v>489151</v>
       </c>
       <c r="R24" t="n">
-        <v>6720114</v>
+        <v>6720086</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3166,7 +3166,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3203,7 +3203,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130800682</v>
+        <v>130800690</v>
       </c>
       <c r="B25" t="n">
         <v>79243</v>
@@ -3238,10 +3238,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>489151</v>
+        <v>489198</v>
       </c>
       <c r="R25" t="n">
-        <v>6720086</v>
+        <v>6720010</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3273,7 +3273,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3524,7 +3524,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130800695</v>
+        <v>130800687</v>
       </c>
       <c r="B28" t="n">
         <v>79243</v>
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>489231</v>
+        <v>489175</v>
       </c>
       <c r="R28" t="n">
-        <v>6719941</v>
+        <v>6720053</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3594,7 +3594,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3604,7 +3604,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3631,7 +3631,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130800687</v>
+        <v>130800695</v>
       </c>
       <c r="B29" t="n">
         <v>79243</v>
@@ -3666,10 +3666,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>489175</v>
+        <v>489231</v>
       </c>
       <c r="R29" t="n">
-        <v>6720053</v>
+        <v>6719941</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3701,7 +3701,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3845,7 +3845,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130800688</v>
+        <v>130800716</v>
       </c>
       <c r="B31" t="n">
         <v>79243</v>
@@ -3880,10 +3880,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>489168</v>
+        <v>489172</v>
       </c>
       <c r="R31" t="n">
-        <v>6720046</v>
+        <v>6720145</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3915,7 +3915,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3925,7 +3925,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3952,7 +3952,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130800678</v>
+        <v>130800688</v>
       </c>
       <c r="B32" t="n">
         <v>79243</v>
@@ -3987,10 +3987,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>489131</v>
+        <v>489168</v>
       </c>
       <c r="R32" t="n">
-        <v>6720117</v>
+        <v>6720046</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4032,7 +4032,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4059,7 +4059,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130800716</v>
+        <v>130800678</v>
       </c>
       <c r="B33" t="n">
         <v>79243</v>
@@ -4094,10 +4094,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>489172</v>
+        <v>489131</v>
       </c>
       <c r="R33" t="n">
-        <v>6720145</v>
+        <v>6720117</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4139,7 +4139,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4808,7 +4808,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130800714</v>
+        <v>130800707</v>
       </c>
       <c r="B40" t="n">
         <v>79243</v>
@@ -4843,10 +4843,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>489163</v>
+        <v>489119</v>
       </c>
       <c r="R40" t="n">
-        <v>6720122</v>
+        <v>6720040</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4878,7 +4878,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4915,7 +4915,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130800707</v>
+        <v>130800677</v>
       </c>
       <c r="B41" t="n">
         <v>79243</v>
@@ -4950,10 +4950,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>489119</v>
+        <v>489132</v>
       </c>
       <c r="R41" t="n">
-        <v>6720040</v>
+        <v>6720123</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4985,7 +4985,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4995,7 +4995,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5022,7 +5022,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130800677</v>
+        <v>130800714</v>
       </c>
       <c r="B42" t="n">
         <v>79243</v>
@@ -5057,10 +5057,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>489132</v>
+        <v>489163</v>
       </c>
       <c r="R42" t="n">
-        <v>6720123</v>
+        <v>6720122</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5092,7 +5092,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5102,7 +5102,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5236,7 +5236,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130800681</v>
+        <v>130800667</v>
       </c>
       <c r="B44" t="n">
         <v>79243</v>
@@ -5271,10 +5271,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>489138</v>
+        <v>489199</v>
       </c>
       <c r="R44" t="n">
-        <v>6720092</v>
+        <v>6720176</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5450,7 +5450,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130800667</v>
+        <v>130800681</v>
       </c>
       <c r="B46" t="n">
         <v>79243</v>
@@ -5485,10 +5485,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>489199</v>
+        <v>489138</v>
       </c>
       <c r="R46" t="n">
-        <v>6720176</v>
+        <v>6720092</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5520,7 +5520,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5530,7 +5530,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5664,10 +5664,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130800610</v>
+        <v>130800704</v>
       </c>
       <c r="B48" t="n">
-        <v>91808</v>
+        <v>79243</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5675,21 +5675,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5699,10 +5699,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>489216</v>
+        <v>489180</v>
       </c>
       <c r="R48" t="n">
-        <v>6719995</v>
+        <v>6719972</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5734,7 +5734,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5744,7 +5744,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5771,10 +5771,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130800704</v>
+        <v>130800610</v>
       </c>
       <c r="B49" t="n">
-        <v>79243</v>
+        <v>91808</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5782,21 +5782,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5806,10 +5806,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>489180</v>
+        <v>489216</v>
       </c>
       <c r="R49" t="n">
-        <v>6719972</v>
+        <v>6719995</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5841,7 +5841,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6418,45 +6418,50 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130800683</v>
+        <v>130800637</v>
       </c>
       <c r="B55" t="n">
-        <v>79243</v>
+        <v>8451</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>489169</v>
+        <v>489091</v>
       </c>
       <c r="R55" t="n">
-        <v>6720075</v>
+        <v>6720083</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6488,7 +6493,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6498,7 +6503,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6507,6 +6512,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6525,50 +6531,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130800637</v>
+        <v>130800683</v>
       </c>
       <c r="B56" t="n">
-        <v>8451</v>
+        <v>79243</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>489091</v>
+        <v>489169</v>
       </c>
       <c r="R56" t="n">
-        <v>6720083</v>
+        <v>6720075</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6600,7 +6601,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6610,7 +6611,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6619,7 +6620,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6638,45 +6638,50 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130800691</v>
+        <v>130800604</v>
       </c>
       <c r="B57" t="n">
-        <v>79243</v>
+        <v>5197</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>105930</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>489214</v>
+        <v>489244</v>
       </c>
       <c r="R57" t="n">
-        <v>6720016</v>
+        <v>6719935</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6708,7 +6713,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6718,7 +6723,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6745,50 +6750,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130800604</v>
+        <v>130800705</v>
       </c>
       <c r="B58" t="n">
-        <v>5197</v>
+        <v>79243</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>489244</v>
+        <v>489144</v>
       </c>
       <c r="R58" t="n">
-        <v>6719935</v>
+        <v>6719996</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6820,7 +6820,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6830,7 +6830,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6857,10 +6857,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130800702</v>
+        <v>130800619</v>
       </c>
       <c r="B59" t="n">
-        <v>79243</v>
+        <v>57881</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6868,34 +6868,39 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>489258</v>
+        <v>489184</v>
       </c>
       <c r="R59" t="n">
-        <v>6719949</v>
+        <v>6720170</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6927,7 +6932,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6937,7 +6942,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6964,7 +6969,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130800705</v>
+        <v>130800691</v>
       </c>
       <c r="B60" t="n">
         <v>79243</v>
@@ -6999,10 +7004,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>489144</v>
+        <v>489214</v>
       </c>
       <c r="R60" t="n">
-        <v>6719996</v>
+        <v>6720016</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7034,7 +7039,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7044,7 +7049,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7071,10 +7076,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130800619</v>
+        <v>130800702</v>
       </c>
       <c r="B61" t="n">
-        <v>57881</v>
+        <v>79243</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7082,39 +7087,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>489184</v>
+        <v>489258</v>
       </c>
       <c r="R61" t="n">
-        <v>6720170</v>
+        <v>6719949</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7146,7 +7146,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7156,7 +7156,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7616,7 +7616,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130800694</v>
+        <v>130800692</v>
       </c>
       <c r="B66" t="n">
         <v>79243</v>
@@ -7651,10 +7651,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>489214</v>
+        <v>489211</v>
       </c>
       <c r="R66" t="n">
-        <v>6719991</v>
+        <v>6720011</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7686,7 +7686,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7696,7 +7696,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7723,7 +7723,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130800692</v>
+        <v>130800694</v>
       </c>
       <c r="B67" t="n">
         <v>79243</v>
@@ -7758,10 +7758,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>489211</v>
+        <v>489214</v>
       </c>
       <c r="R67" t="n">
-        <v>6720011</v>
+        <v>6719991</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7793,7 +7793,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7803,7 +7803,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7830,10 +7830,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130800711</v>
+        <v>130800620</v>
       </c>
       <c r="B68" t="n">
-        <v>79243</v>
+        <v>57881</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7841,34 +7841,39 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>489138</v>
+        <v>489144</v>
       </c>
       <c r="R68" t="n">
-        <v>6720109</v>
+        <v>6720087</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7900,7 +7905,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7910,7 +7915,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7937,10 +7942,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130800620</v>
+        <v>130800711</v>
       </c>
       <c r="B69" t="n">
-        <v>57881</v>
+        <v>79243</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7948,39 +7953,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>489144</v>
+        <v>489138</v>
       </c>
       <c r="R69" t="n">
-        <v>6720087</v>
+        <v>6720109</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8012,7 +8012,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8022,7 +8022,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD69" t="b">

--- a/artfynd/A 62861-2025 artfynd.xlsx
+++ b/artfynd/A 62861-2025 artfynd.xlsx
@@ -1250,7 +1250,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130800713</v>
+        <v>130800726</v>
       </c>
       <c r="B7" t="n">
         <v>79243</v>
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>489149</v>
+        <v>489323</v>
       </c>
       <c r="R7" t="n">
-        <v>6720123</v>
+        <v>6720025</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,7 +1357,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130800726</v>
+        <v>130800713</v>
       </c>
       <c r="B8" t="n">
         <v>79243</v>
@@ -1392,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>489323</v>
+        <v>489149</v>
       </c>
       <c r="R8" t="n">
-        <v>6720025</v>
+        <v>6720123</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1464,7 +1464,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130800693</v>
+        <v>130800706</v>
       </c>
       <c r="B9" t="n">
         <v>79243</v>
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>489211</v>
+        <v>489143</v>
       </c>
       <c r="R9" t="n">
-        <v>6720001</v>
+        <v>6720009</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130800627</v>
+        <v>130800693</v>
       </c>
       <c r="B10" t="n">
-        <v>57881</v>
+        <v>79243</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1582,39 +1582,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>489163</v>
+        <v>489211</v>
       </c>
       <c r="R10" t="n">
-        <v>6719987</v>
+        <v>6720001</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1646,7 +1641,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,7 +1651,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,10 +1678,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130800622</v>
+        <v>130800672</v>
       </c>
       <c r="B11" t="n">
-        <v>57881</v>
+        <v>79243</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1694,39 +1689,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>489171</v>
+        <v>489170</v>
       </c>
       <c r="R11" t="n">
-        <v>6720048</v>
+        <v>6720188</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1758,7 +1748,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1768,7 +1758,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,7 +1785,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130800706</v>
+        <v>130800721</v>
       </c>
       <c r="B12" t="n">
         <v>79243</v>
@@ -1830,10 +1820,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>489143</v>
+        <v>489189</v>
       </c>
       <c r="R12" t="n">
-        <v>6720009</v>
+        <v>6720073</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1865,7 +1855,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1875,7 +1865,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1902,10 +1892,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130800721</v>
+        <v>130800627</v>
       </c>
       <c r="B13" t="n">
-        <v>79243</v>
+        <v>57881</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1913,34 +1903,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>489189</v>
+        <v>489163</v>
       </c>
       <c r="R13" t="n">
-        <v>6720073</v>
+        <v>6719987</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1972,7 +1967,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1982,7 +1977,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2009,10 +2004,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130800672</v>
+        <v>130800622</v>
       </c>
       <c r="B14" t="n">
-        <v>79243</v>
+        <v>57881</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2020,34 +2015,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>489170</v>
+        <v>489171</v>
       </c>
       <c r="R14" t="n">
-        <v>6720188</v>
+        <v>6720048</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2079,7 +2079,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2116,7 +2116,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130800689</v>
+        <v>130800671</v>
       </c>
       <c r="B15" t="n">
         <v>79243</v>
@@ -2151,10 +2151,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>489171</v>
+        <v>489159</v>
       </c>
       <c r="R15" t="n">
-        <v>6720037</v>
+        <v>6720170</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2223,7 +2223,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130800634</v>
+        <v>130800641</v>
       </c>
       <c r="B16" t="n">
         <v>8451</v>
@@ -2263,10 +2263,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>489196</v>
+        <v>489210</v>
       </c>
       <c r="R16" t="n">
-        <v>6720103</v>
+        <v>6720036</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2308,7 +2308,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2336,45 +2336,50 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130800609</v>
+        <v>130800634</v>
       </c>
       <c r="B17" t="n">
-        <v>91808</v>
+        <v>8451</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>489172</v>
+        <v>489196</v>
       </c>
       <c r="R17" t="n">
-        <v>6720186</v>
+        <v>6720103</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2406,7 +2411,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2416,7 +2421,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2425,6 +2430,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2443,10 +2449,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130800671</v>
+        <v>130800609</v>
       </c>
       <c r="B18" t="n">
-        <v>79243</v>
+        <v>91808</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2454,21 +2460,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2478,10 +2484,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>489159</v>
+        <v>489172</v>
       </c>
       <c r="R18" t="n">
-        <v>6720170</v>
+        <v>6720186</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2513,7 +2519,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2523,7 +2529,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2550,50 +2556,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130800641</v>
+        <v>130800689</v>
       </c>
       <c r="B19" t="n">
-        <v>8451</v>
+        <v>79243</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>489210</v>
+        <v>489171</v>
       </c>
       <c r="R19" t="n">
-        <v>6720036</v>
+        <v>6720037</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2625,7 +2626,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2635,7 +2636,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2644,7 +2645,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -3096,7 +3096,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130800682</v>
+        <v>130800690</v>
       </c>
       <c r="B24" t="n">
         <v>79243</v>
@@ -3131,10 +3131,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>489151</v>
+        <v>489198</v>
       </c>
       <c r="R24" t="n">
-        <v>6720086</v>
+        <v>6720010</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3166,7 +3166,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3203,7 +3203,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130800690</v>
+        <v>130800682</v>
       </c>
       <c r="B25" t="n">
         <v>79243</v>
@@ -3238,10 +3238,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>489198</v>
+        <v>489151</v>
       </c>
       <c r="R25" t="n">
-        <v>6720010</v>
+        <v>6720086</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3273,7 +3273,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3310,32 +3310,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130800606</v>
+        <v>130800687</v>
       </c>
       <c r="B26" t="n">
-        <v>92179</v>
+        <v>79243</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3345,10 +3345,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>489169</v>
+        <v>489175</v>
       </c>
       <c r="R26" t="n">
-        <v>6720185</v>
+        <v>6720053</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3380,7 +3380,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3390,7 +3390,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3417,7 +3417,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130800696</v>
+        <v>130800725</v>
       </c>
       <c r="B27" t="n">
         <v>79243</v>
@@ -3452,10 +3452,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>489243</v>
+        <v>489332</v>
       </c>
       <c r="R27" t="n">
-        <v>6719933</v>
+        <v>6720052</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3487,7 +3487,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3524,7 +3524,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130800687</v>
+        <v>130800696</v>
       </c>
       <c r="B28" t="n">
         <v>79243</v>
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>489175</v>
+        <v>489243</v>
       </c>
       <c r="R28" t="n">
-        <v>6720053</v>
+        <v>6719933</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3594,7 +3594,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3604,7 +3604,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3738,32 +3738,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130800725</v>
+        <v>130800606</v>
       </c>
       <c r="B30" t="n">
-        <v>79243</v>
+        <v>92179</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3773,10 +3773,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>489332</v>
+        <v>489169</v>
       </c>
       <c r="R30" t="n">
-        <v>6720052</v>
+        <v>6720185</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3808,7 +3808,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3818,7 +3818,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3845,7 +3845,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130800716</v>
+        <v>130800688</v>
       </c>
       <c r="B31" t="n">
         <v>79243</v>
@@ -3880,10 +3880,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>489172</v>
+        <v>489168</v>
       </c>
       <c r="R31" t="n">
-        <v>6720145</v>
+        <v>6720046</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3915,7 +3915,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3925,7 +3925,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3952,7 +3952,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130800688</v>
+        <v>130800678</v>
       </c>
       <c r="B32" t="n">
         <v>79243</v>
@@ -3987,10 +3987,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>489168</v>
+        <v>489131</v>
       </c>
       <c r="R32" t="n">
-        <v>6720046</v>
+        <v>6720117</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4032,7 +4032,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4059,7 +4059,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130800678</v>
+        <v>130800716</v>
       </c>
       <c r="B33" t="n">
         <v>79243</v>
@@ -4094,10 +4094,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>489131</v>
+        <v>489172</v>
       </c>
       <c r="R33" t="n">
-        <v>6720117</v>
+        <v>6720145</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4139,7 +4139,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4701,32 +4701,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130800608</v>
+        <v>130800714</v>
       </c>
       <c r="B39" t="n">
-        <v>92179</v>
+        <v>79243</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4736,10 +4736,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>489214</v>
+        <v>489163</v>
       </c>
       <c r="R39" t="n">
-        <v>6719996</v>
+        <v>6720122</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4771,7 +4771,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4808,32 +4808,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130800707</v>
+        <v>130800608</v>
       </c>
       <c r="B40" t="n">
-        <v>79243</v>
+        <v>92179</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4843,10 +4843,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>489119</v>
+        <v>489214</v>
       </c>
       <c r="R40" t="n">
-        <v>6720040</v>
+        <v>6719996</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4878,7 +4878,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4915,7 +4915,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130800677</v>
+        <v>130800707</v>
       </c>
       <c r="B41" t="n">
         <v>79243</v>
@@ -4950,10 +4950,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>489132</v>
+        <v>489119</v>
       </c>
       <c r="R41" t="n">
-        <v>6720123</v>
+        <v>6720040</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4985,7 +4985,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4995,7 +4995,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5022,7 +5022,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130800714</v>
+        <v>130800677</v>
       </c>
       <c r="B42" t="n">
         <v>79243</v>
@@ -5057,10 +5057,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>489163</v>
+        <v>489132</v>
       </c>
       <c r="R42" t="n">
-        <v>6720122</v>
+        <v>6720123</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5092,7 +5092,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5102,7 +5102,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5129,7 +5129,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130800709</v>
+        <v>130800684</v>
       </c>
       <c r="B43" t="n">
         <v>79243</v>
@@ -5164,10 +5164,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>489094</v>
+        <v>489177</v>
       </c>
       <c r="R43" t="n">
-        <v>6720086</v>
+        <v>6720066</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5199,7 +5199,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5209,7 +5209,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5236,7 +5236,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130800667</v>
+        <v>130800681</v>
       </c>
       <c r="B44" t="n">
         <v>79243</v>
@@ -5271,10 +5271,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>489199</v>
+        <v>489138</v>
       </c>
       <c r="R44" t="n">
-        <v>6720176</v>
+        <v>6720092</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5343,7 +5343,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130800684</v>
+        <v>130800709</v>
       </c>
       <c r="B45" t="n">
         <v>79243</v>
@@ -5378,10 +5378,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>489177</v>
+        <v>489094</v>
       </c>
       <c r="R45" t="n">
-        <v>6720066</v>
+        <v>6720086</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5423,7 +5423,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5450,7 +5450,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130800681</v>
+        <v>130800667</v>
       </c>
       <c r="B46" t="n">
         <v>79243</v>
@@ -5485,10 +5485,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>489138</v>
+        <v>489199</v>
       </c>
       <c r="R46" t="n">
-        <v>6720092</v>
+        <v>6720176</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5520,7 +5520,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5530,7 +5530,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5771,10 +5771,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130800610</v>
+        <v>130800715</v>
       </c>
       <c r="B49" t="n">
-        <v>91808</v>
+        <v>79243</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5782,21 +5782,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5806,10 +5806,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>489216</v>
+        <v>489166</v>
       </c>
       <c r="R49" t="n">
-        <v>6719995</v>
+        <v>6720127</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5841,7 +5841,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5878,10 +5878,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130800715</v>
+        <v>130800610</v>
       </c>
       <c r="B50" t="n">
-        <v>79243</v>
+        <v>91808</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5889,21 +5889,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5913,10 +5913,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>489166</v>
+        <v>489216</v>
       </c>
       <c r="R50" t="n">
-        <v>6720127</v>
+        <v>6719995</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5948,7 +5948,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6311,45 +6311,50 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130800680</v>
+        <v>130800637</v>
       </c>
       <c r="B54" t="n">
-        <v>79243</v>
+        <v>8451</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>489131</v>
+        <v>489091</v>
       </c>
       <c r="R54" t="n">
-        <v>6720110</v>
+        <v>6720083</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6381,7 +6386,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6391,7 +6396,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6400,6 +6405,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6418,50 +6424,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130800637</v>
+        <v>130800680</v>
       </c>
       <c r="B55" t="n">
-        <v>8451</v>
+        <v>79243</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>489091</v>
+        <v>489131</v>
       </c>
       <c r="R55" t="n">
-        <v>6720083</v>
+        <v>6720110</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6493,7 +6494,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6503,7 +6504,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6512,7 +6513,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6638,50 +6638,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130800604</v>
+        <v>130800708</v>
       </c>
       <c r="B57" t="n">
-        <v>5197</v>
+        <v>79243</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>489244</v>
+        <v>489077</v>
       </c>
       <c r="R57" t="n">
-        <v>6719935</v>
+        <v>6720065</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6713,7 +6708,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6723,7 +6718,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6750,45 +6745,50 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130800705</v>
+        <v>130800768</v>
       </c>
       <c r="B58" t="n">
-        <v>79243</v>
+        <v>5177</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>489144</v>
+        <v>489234</v>
       </c>
       <c r="R58" t="n">
-        <v>6719996</v>
+        <v>6719934</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6820,7 +6820,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6830,7 +6830,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7183,7 +7183,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130800708</v>
+        <v>130800705</v>
       </c>
       <c r="B62" t="n">
         <v>79243</v>
@@ -7218,10 +7218,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>489077</v>
+        <v>489144</v>
       </c>
       <c r="R62" t="n">
-        <v>6720065</v>
+        <v>6719996</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7253,7 +7253,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7263,7 +7263,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7290,10 +7290,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130800768</v>
+        <v>130800604</v>
       </c>
       <c r="B63" t="n">
-        <v>5177</v>
+        <v>5197</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7301,27 +7301,27 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -7330,10 +7330,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>489234</v>
+        <v>489244</v>
       </c>
       <c r="R63" t="n">
-        <v>6719934</v>
+        <v>6719935</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7365,7 +7365,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7375,7 +7375,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7616,7 +7616,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130800692</v>
+        <v>130800694</v>
       </c>
       <c r="B66" t="n">
         <v>79243</v>
@@ -7651,10 +7651,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>489211</v>
+        <v>489214</v>
       </c>
       <c r="R66" t="n">
-        <v>6720011</v>
+        <v>6719991</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7686,7 +7686,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7696,7 +7696,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7723,7 +7723,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130800694</v>
+        <v>130800692</v>
       </c>
       <c r="B67" t="n">
         <v>79243</v>
@@ -7758,10 +7758,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>489214</v>
+        <v>489211</v>
       </c>
       <c r="R67" t="n">
-        <v>6719991</v>
+        <v>6720011</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7793,7 +7793,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7803,7 +7803,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD67" t="b">

--- a/artfynd/A 62861-2025 artfynd.xlsx
+++ b/artfynd/A 62861-2025 artfynd.xlsx
@@ -1250,7 +1250,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130800726</v>
+        <v>130800713</v>
       </c>
       <c r="B7" t="n">
         <v>79243</v>
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>489323</v>
+        <v>489149</v>
       </c>
       <c r="R7" t="n">
-        <v>6720025</v>
+        <v>6720123</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,7 +1357,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130800713</v>
+        <v>130800726</v>
       </c>
       <c r="B8" t="n">
         <v>79243</v>
@@ -1392,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>489149</v>
+        <v>489323</v>
       </c>
       <c r="R8" t="n">
-        <v>6720123</v>
+        <v>6720025</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1571,7 +1571,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130800693</v>
+        <v>130800721</v>
       </c>
       <c r="B10" t="n">
         <v>79243</v>
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>489211</v>
+        <v>489189</v>
       </c>
       <c r="R10" t="n">
-        <v>6720001</v>
+        <v>6720073</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1678,7 +1678,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130800672</v>
+        <v>130800693</v>
       </c>
       <c r="B11" t="n">
         <v>79243</v>
@@ -1713,10 +1713,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>489170</v>
+        <v>489211</v>
       </c>
       <c r="R11" t="n">
-        <v>6720188</v>
+        <v>6720001</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1785,7 +1785,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130800721</v>
+        <v>130800672</v>
       </c>
       <c r="B12" t="n">
         <v>79243</v>
@@ -1820,10 +1820,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>489189</v>
+        <v>489170</v>
       </c>
       <c r="R12" t="n">
-        <v>6720073</v>
+        <v>6720188</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1865,7 +1865,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2116,10 +2116,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130800671</v>
+        <v>130800609</v>
       </c>
       <c r="B15" t="n">
-        <v>79243</v>
+        <v>91808</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2127,21 +2127,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2151,10 +2151,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>489159</v>
+        <v>489172</v>
       </c>
       <c r="R15" t="n">
-        <v>6720170</v>
+        <v>6720186</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2223,50 +2223,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130800641</v>
+        <v>130800671</v>
       </c>
       <c r="B16" t="n">
-        <v>8451</v>
+        <v>79243</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>489210</v>
+        <v>489159</v>
       </c>
       <c r="R16" t="n">
-        <v>6720036</v>
+        <v>6720170</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2298,7 +2293,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2308,7 +2303,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2317,7 +2312,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2336,50 +2330,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130800634</v>
+        <v>130800689</v>
       </c>
       <c r="B17" t="n">
-        <v>8451</v>
+        <v>79243</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>489196</v>
+        <v>489171</v>
       </c>
       <c r="R17" t="n">
-        <v>6720103</v>
+        <v>6720037</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2411,7 +2400,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2421,7 +2410,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2430,7 +2419,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2449,45 +2437,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130800609</v>
+        <v>130800641</v>
       </c>
       <c r="B18" t="n">
-        <v>91808</v>
+        <v>8451</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>489172</v>
+        <v>489210</v>
       </c>
       <c r="R18" t="n">
-        <v>6720186</v>
+        <v>6720036</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2519,7 +2512,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2529,7 +2522,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2538,6 +2531,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2556,45 +2550,50 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130800689</v>
+        <v>130800634</v>
       </c>
       <c r="B19" t="n">
-        <v>79243</v>
+        <v>8451</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>489171</v>
+        <v>489196</v>
       </c>
       <c r="R19" t="n">
-        <v>6720037</v>
+        <v>6720103</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2626,7 +2625,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2636,7 +2635,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2645,6 +2644,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2663,10 +2663,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130800621</v>
+        <v>130800710</v>
       </c>
       <c r="B20" t="n">
-        <v>57881</v>
+        <v>79243</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2674,39 +2674,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>489175</v>
+        <v>489124</v>
       </c>
       <c r="R20" t="n">
-        <v>6720065</v>
+        <v>6720109</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2738,7 +2733,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2748,7 +2743,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2882,10 +2877,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130800710</v>
+        <v>130800621</v>
       </c>
       <c r="B22" t="n">
-        <v>79243</v>
+        <v>57881</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2893,34 +2888,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>489124</v>
+        <v>489175</v>
       </c>
       <c r="R22" t="n">
-        <v>6720109</v>
+        <v>6720065</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2952,7 +2952,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2989,7 +2989,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130800718</v>
+        <v>130800690</v>
       </c>
       <c r="B23" t="n">
         <v>79243</v>
@@ -3024,10 +3024,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>489189</v>
+        <v>489198</v>
       </c>
       <c r="R23" t="n">
-        <v>6720114</v>
+        <v>6720010</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3096,7 +3096,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130800690</v>
+        <v>130800718</v>
       </c>
       <c r="B24" t="n">
         <v>79243</v>
@@ -3131,10 +3131,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>489198</v>
+        <v>489189</v>
       </c>
       <c r="R24" t="n">
-        <v>6720010</v>
+        <v>6720114</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3166,7 +3166,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3310,32 +3310,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130800687</v>
+        <v>130800606</v>
       </c>
       <c r="B26" t="n">
-        <v>79243</v>
+        <v>92179</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3345,10 +3345,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>489175</v>
+        <v>489169</v>
       </c>
       <c r="R26" t="n">
-        <v>6720053</v>
+        <v>6720185</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3380,7 +3380,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3390,7 +3390,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3524,7 +3524,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130800696</v>
+        <v>130800695</v>
       </c>
       <c r="B28" t="n">
         <v>79243</v>
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>489243</v>
+        <v>489231</v>
       </c>
       <c r="R28" t="n">
-        <v>6719933</v>
+        <v>6719941</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3594,7 +3594,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3604,7 +3604,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3631,7 +3631,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130800695</v>
+        <v>130800687</v>
       </c>
       <c r="B29" t="n">
         <v>79243</v>
@@ -3666,10 +3666,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>489231</v>
+        <v>489175</v>
       </c>
       <c r="R29" t="n">
-        <v>6719941</v>
+        <v>6720053</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3701,7 +3701,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3738,32 +3738,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130800606</v>
+        <v>130800696</v>
       </c>
       <c r="B30" t="n">
-        <v>92179</v>
+        <v>79243</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3773,10 +3773,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>489169</v>
+        <v>489243</v>
       </c>
       <c r="R30" t="n">
-        <v>6720185</v>
+        <v>6719933</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3808,7 +3808,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3818,7 +3818,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4166,7 +4166,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130800669</v>
+        <v>130800712</v>
       </c>
       <c r="B34" t="n">
         <v>79243</v>
@@ -4201,10 +4201,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>489170</v>
+        <v>489143</v>
       </c>
       <c r="R34" t="n">
-        <v>6720167</v>
+        <v>6720114</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4236,7 +4236,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4246,7 +4246,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4273,7 +4273,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130800712</v>
+        <v>130800669</v>
       </c>
       <c r="B35" t="n">
         <v>79243</v>
@@ -4308,10 +4308,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>489143</v>
+        <v>489170</v>
       </c>
       <c r="R35" t="n">
-        <v>6720114</v>
+        <v>6720167</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4343,7 +4343,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4353,7 +4353,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4380,7 +4380,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130800679</v>
+        <v>130800676</v>
       </c>
       <c r="B36" t="n">
         <v>79243</v>
@@ -4415,10 +4415,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>489122</v>
+        <v>489151</v>
       </c>
       <c r="R36" t="n">
-        <v>6720120</v>
+        <v>6720144</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4450,7 +4450,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4460,7 +4460,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4487,7 +4487,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130800676</v>
+        <v>130800679</v>
       </c>
       <c r="B37" t="n">
         <v>79243</v>
@@ -4522,10 +4522,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>489151</v>
+        <v>489122</v>
       </c>
       <c r="R37" t="n">
-        <v>6720144</v>
+        <v>6720120</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4557,7 +4557,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4567,7 +4567,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4701,32 +4701,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130800714</v>
+        <v>130800608</v>
       </c>
       <c r="B39" t="n">
-        <v>79243</v>
+        <v>92179</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4736,10 +4736,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>489163</v>
+        <v>489214</v>
       </c>
       <c r="R39" t="n">
-        <v>6720122</v>
+        <v>6719996</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4771,7 +4771,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4808,32 +4808,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130800608</v>
+        <v>130800707</v>
       </c>
       <c r="B40" t="n">
-        <v>92179</v>
+        <v>79243</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4843,10 +4843,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>489214</v>
+        <v>489119</v>
       </c>
       <c r="R40" t="n">
-        <v>6719996</v>
+        <v>6720040</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4878,7 +4878,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4915,7 +4915,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130800707</v>
+        <v>130800714</v>
       </c>
       <c r="B41" t="n">
         <v>79243</v>
@@ -4950,10 +4950,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>489119</v>
+        <v>489163</v>
       </c>
       <c r="R41" t="n">
-        <v>6720040</v>
+        <v>6720122</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4985,7 +4985,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4995,7 +4995,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5236,7 +5236,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130800681</v>
+        <v>130800709</v>
       </c>
       <c r="B44" t="n">
         <v>79243</v>
@@ -5271,10 +5271,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>489138</v>
+        <v>489094</v>
       </c>
       <c r="R44" t="n">
-        <v>6720092</v>
+        <v>6720086</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5343,7 +5343,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130800709</v>
+        <v>130800667</v>
       </c>
       <c r="B45" t="n">
         <v>79243</v>
@@ -5378,10 +5378,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>489094</v>
+        <v>489199</v>
       </c>
       <c r="R45" t="n">
-        <v>6720086</v>
+        <v>6720176</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5423,7 +5423,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5450,7 +5450,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130800667</v>
+        <v>130800681</v>
       </c>
       <c r="B46" t="n">
         <v>79243</v>
@@ -5485,10 +5485,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>489199</v>
+        <v>489138</v>
       </c>
       <c r="R46" t="n">
-        <v>6720176</v>
+        <v>6720092</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5520,7 +5520,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5530,7 +5530,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5664,10 +5664,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130800704</v>
+        <v>130800610</v>
       </c>
       <c r="B48" t="n">
-        <v>79243</v>
+        <v>91808</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5675,21 +5675,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5699,10 +5699,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>489180</v>
+        <v>489216</v>
       </c>
       <c r="R48" t="n">
-        <v>6719972</v>
+        <v>6719995</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5734,7 +5734,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5744,7 +5744,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5771,7 +5771,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130800715</v>
+        <v>130800704</v>
       </c>
       <c r="B49" t="n">
         <v>79243</v>
@@ -5806,10 +5806,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>489166</v>
+        <v>489180</v>
       </c>
       <c r="R49" t="n">
-        <v>6720127</v>
+        <v>6719972</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5841,7 +5841,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5878,10 +5878,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130800610</v>
+        <v>130800715</v>
       </c>
       <c r="B50" t="n">
-        <v>91808</v>
+        <v>79243</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5889,21 +5889,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5913,10 +5913,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>489216</v>
+        <v>489166</v>
       </c>
       <c r="R50" t="n">
-        <v>6719995</v>
+        <v>6720127</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5948,7 +5948,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5985,10 +5985,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130800630</v>
+        <v>130800673</v>
       </c>
       <c r="B51" t="n">
-        <v>57881</v>
+        <v>79243</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5996,39 +5996,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>489207</v>
+        <v>489180</v>
       </c>
       <c r="R51" t="n">
-        <v>6720041</v>
+        <v>6720180</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6060,7 +6055,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6070,7 +6065,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6097,10 +6092,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130800673</v>
+        <v>130800630</v>
       </c>
       <c r="B52" t="n">
-        <v>79243</v>
+        <v>57881</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6108,34 +6103,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>489180</v>
+        <v>489207</v>
       </c>
       <c r="R52" t="n">
-        <v>6720180</v>
+        <v>6720041</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6167,7 +6167,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6177,7 +6177,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6311,50 +6311,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130800637</v>
+        <v>130800683</v>
       </c>
       <c r="B54" t="n">
-        <v>8451</v>
+        <v>79243</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>489091</v>
+        <v>489169</v>
       </c>
       <c r="R54" t="n">
-        <v>6720083</v>
+        <v>6720075</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6386,7 +6381,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6396,7 +6391,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6405,7 +6400,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6424,45 +6418,50 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130800680</v>
+        <v>130800637</v>
       </c>
       <c r="B55" t="n">
-        <v>79243</v>
+        <v>8451</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>489131</v>
+        <v>489091</v>
       </c>
       <c r="R55" t="n">
-        <v>6720110</v>
+        <v>6720083</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6494,7 +6493,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6504,7 +6503,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6513,6 +6512,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6531,7 +6531,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130800683</v>
+        <v>130800680</v>
       </c>
       <c r="B56" t="n">
         <v>79243</v>
@@ -6566,10 +6566,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>489169</v>
+        <v>489131</v>
       </c>
       <c r="R56" t="n">
-        <v>6720075</v>
+        <v>6720110</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6638,7 +6638,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130800708</v>
+        <v>130800702</v>
       </c>
       <c r="B57" t="n">
         <v>79243</v>
@@ -6673,10 +6673,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>489077</v>
+        <v>489258</v>
       </c>
       <c r="R57" t="n">
-        <v>6720065</v>
+        <v>6719949</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6708,7 +6708,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6718,7 +6718,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6745,50 +6745,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130800768</v>
+        <v>130800708</v>
       </c>
       <c r="B58" t="n">
-        <v>5177</v>
+        <v>79243</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>489234</v>
+        <v>489077</v>
       </c>
       <c r="R58" t="n">
-        <v>6719934</v>
+        <v>6720065</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6820,7 +6815,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6830,7 +6825,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6857,38 +6852,38 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130800619</v>
+        <v>130800768</v>
       </c>
       <c r="B59" t="n">
-        <v>57881</v>
+        <v>5177</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -6897,10 +6892,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>489184</v>
+        <v>489234</v>
       </c>
       <c r="R59" t="n">
-        <v>6720170</v>
+        <v>6719934</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6932,7 +6927,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6942,7 +6937,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6969,45 +6964,50 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130800691</v>
+        <v>130800604</v>
       </c>
       <c r="B60" t="n">
-        <v>79243</v>
+        <v>5197</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>105930</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>489214</v>
+        <v>489244</v>
       </c>
       <c r="R60" t="n">
-        <v>6720016</v>
+        <v>6719935</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7039,7 +7039,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7076,10 +7076,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130800702</v>
+        <v>130800619</v>
       </c>
       <c r="B61" t="n">
-        <v>79243</v>
+        <v>57881</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7087,34 +7087,39 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>489258</v>
+        <v>489184</v>
       </c>
       <c r="R61" t="n">
-        <v>6719949</v>
+        <v>6720170</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7146,7 +7151,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7156,7 +7161,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7183,7 +7188,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130800705</v>
+        <v>130800691</v>
       </c>
       <c r="B62" t="n">
         <v>79243</v>
@@ -7218,10 +7223,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>489144</v>
+        <v>489214</v>
       </c>
       <c r="R62" t="n">
-        <v>6719996</v>
+        <v>6720016</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7253,7 +7258,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7263,7 +7268,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7290,50 +7295,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130800604</v>
+        <v>130800705</v>
       </c>
       <c r="B63" t="n">
-        <v>5197</v>
+        <v>79243</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>489244</v>
+        <v>489144</v>
       </c>
       <c r="R63" t="n">
-        <v>6719935</v>
+        <v>6719996</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7365,7 +7365,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7375,7 +7375,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7402,7 +7402,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130800674</v>
+        <v>130800692</v>
       </c>
       <c r="B64" t="n">
         <v>79243</v>
@@ -7437,10 +7437,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>489168</v>
+        <v>489211</v>
       </c>
       <c r="R64" t="n">
-        <v>6720197</v>
+        <v>6720011</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7472,7 +7472,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7482,7 +7482,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7509,7 +7509,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130800665</v>
+        <v>130800674</v>
       </c>
       <c r="B65" t="n">
         <v>79243</v>
@@ -7544,10 +7544,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>489208</v>
+        <v>489168</v>
       </c>
       <c r="R65" t="n">
-        <v>6720188</v>
+        <v>6720197</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7579,7 +7579,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7589,7 +7589,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7616,7 +7616,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130800694</v>
+        <v>130800665</v>
       </c>
       <c r="B66" t="n">
         <v>79243</v>
@@ -7651,10 +7651,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>489214</v>
+        <v>489208</v>
       </c>
       <c r="R66" t="n">
-        <v>6719991</v>
+        <v>6720188</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7686,7 +7686,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7696,7 +7696,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7723,7 +7723,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130800692</v>
+        <v>130800694</v>
       </c>
       <c r="B67" t="n">
         <v>79243</v>
@@ -7758,10 +7758,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>489211</v>
+        <v>489214</v>
       </c>
       <c r="R67" t="n">
-        <v>6720011</v>
+        <v>6719991</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7793,7 +7793,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7803,7 +7803,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7830,10 +7830,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130800620</v>
+        <v>130800711</v>
       </c>
       <c r="B68" t="n">
-        <v>57881</v>
+        <v>79243</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7841,39 +7841,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>489144</v>
+        <v>489138</v>
       </c>
       <c r="R68" t="n">
-        <v>6720087</v>
+        <v>6720109</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7905,7 +7900,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7915,7 +7910,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7942,10 +7937,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130800711</v>
+        <v>130800620</v>
       </c>
       <c r="B69" t="n">
-        <v>79243</v>
+        <v>57881</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7953,34 +7948,39 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>489138</v>
+        <v>489144</v>
       </c>
       <c r="R69" t="n">
-        <v>6720109</v>
+        <v>6720087</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8012,7 +8012,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8022,7 +8022,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD69" t="b">

--- a/artfynd/A 62861-2025 artfynd.xlsx
+++ b/artfynd/A 62861-2025 artfynd.xlsx
@@ -1571,7 +1571,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130800721</v>
+        <v>130800693</v>
       </c>
       <c r="B10" t="n">
         <v>79243</v>
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>489189</v>
+        <v>489211</v>
       </c>
       <c r="R10" t="n">
-        <v>6720073</v>
+        <v>6720001</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1678,7 +1678,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130800693</v>
+        <v>130800672</v>
       </c>
       <c r="B11" t="n">
         <v>79243</v>
@@ -1713,10 +1713,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>489211</v>
+        <v>489170</v>
       </c>
       <c r="R11" t="n">
-        <v>6720001</v>
+        <v>6720188</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1785,7 +1785,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130800672</v>
+        <v>130800721</v>
       </c>
       <c r="B12" t="n">
         <v>79243</v>
@@ -1820,10 +1820,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>489170</v>
+        <v>489189</v>
       </c>
       <c r="R12" t="n">
-        <v>6720188</v>
+        <v>6720073</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1865,7 +1865,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2116,10 +2116,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130800609</v>
+        <v>130800671</v>
       </c>
       <c r="B15" t="n">
-        <v>91808</v>
+        <v>79243</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2127,21 +2127,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2151,10 +2151,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>489172</v>
+        <v>489159</v>
       </c>
       <c r="R15" t="n">
-        <v>6720186</v>
+        <v>6720170</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2223,7 +2223,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130800671</v>
+        <v>130800689</v>
       </c>
       <c r="B16" t="n">
         <v>79243</v>
@@ -2258,10 +2258,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>489159</v>
+        <v>489171</v>
       </c>
       <c r="R16" t="n">
-        <v>6720170</v>
+        <v>6720037</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2293,7 +2293,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2330,45 +2330,50 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130800689</v>
+        <v>130800641</v>
       </c>
       <c r="B17" t="n">
-        <v>79243</v>
+        <v>8451</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>489171</v>
+        <v>489210</v>
       </c>
       <c r="R17" t="n">
-        <v>6720037</v>
+        <v>6720036</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2400,7 +2405,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2410,7 +2415,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2419,6 +2424,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2437,7 +2443,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130800641</v>
+        <v>130800634</v>
       </c>
       <c r="B18" t="n">
         <v>8451</v>
@@ -2477,10 +2483,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>489210</v>
+        <v>489196</v>
       </c>
       <c r="R18" t="n">
-        <v>6720036</v>
+        <v>6720103</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2512,7 +2518,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2522,7 +2528,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2550,50 +2556,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130800634</v>
+        <v>130800609</v>
       </c>
       <c r="B19" t="n">
-        <v>8451</v>
+        <v>91808</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>489196</v>
+        <v>489172</v>
       </c>
       <c r="R19" t="n">
-        <v>6720103</v>
+        <v>6720186</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2625,7 +2626,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2635,7 +2636,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2644,7 +2645,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2663,10 +2663,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130800710</v>
+        <v>130800621</v>
       </c>
       <c r="B20" t="n">
-        <v>79243</v>
+        <v>57881</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2674,34 +2674,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>489124</v>
+        <v>489175</v>
       </c>
       <c r="R20" t="n">
-        <v>6720109</v>
+        <v>6720065</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2733,7 +2738,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2743,7 +2748,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2770,7 +2775,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130800668</v>
+        <v>130800710</v>
       </c>
       <c r="B21" t="n">
         <v>79243</v>
@@ -2805,10 +2810,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>489197</v>
+        <v>489124</v>
       </c>
       <c r="R21" t="n">
-        <v>6720167</v>
+        <v>6720109</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2840,7 +2845,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2850,7 +2855,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2877,10 +2882,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130800621</v>
+        <v>130800668</v>
       </c>
       <c r="B22" t="n">
-        <v>57881</v>
+        <v>79243</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2888,39 +2893,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>489175</v>
+        <v>489197</v>
       </c>
       <c r="R22" t="n">
-        <v>6720065</v>
+        <v>6720167</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2952,7 +2952,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3310,32 +3310,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130800606</v>
+        <v>130800695</v>
       </c>
       <c r="B26" t="n">
-        <v>92179</v>
+        <v>79243</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3345,10 +3345,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>489169</v>
+        <v>489231</v>
       </c>
       <c r="R26" t="n">
-        <v>6720185</v>
+        <v>6719941</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3380,7 +3380,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3390,7 +3390,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3417,7 +3417,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130800725</v>
+        <v>130800687</v>
       </c>
       <c r="B27" t="n">
         <v>79243</v>
@@ -3452,10 +3452,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>489332</v>
+        <v>489175</v>
       </c>
       <c r="R27" t="n">
-        <v>6720052</v>
+        <v>6720053</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3487,7 +3487,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3524,7 +3524,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130800695</v>
+        <v>130800725</v>
       </c>
       <c r="B28" t="n">
         <v>79243</v>
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>489231</v>
+        <v>489332</v>
       </c>
       <c r="R28" t="n">
-        <v>6719941</v>
+        <v>6720052</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3594,7 +3594,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3604,7 +3604,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3631,7 +3631,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130800687</v>
+        <v>130800696</v>
       </c>
       <c r="B29" t="n">
         <v>79243</v>
@@ -3666,10 +3666,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>489175</v>
+        <v>489243</v>
       </c>
       <c r="R29" t="n">
-        <v>6720053</v>
+        <v>6719933</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3701,7 +3701,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3738,32 +3738,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130800696</v>
+        <v>130800606</v>
       </c>
       <c r="B30" t="n">
-        <v>79243</v>
+        <v>92179</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3773,10 +3773,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>489243</v>
+        <v>489169</v>
       </c>
       <c r="R30" t="n">
-        <v>6719933</v>
+        <v>6720185</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3808,7 +3808,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3818,7 +3818,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4166,7 +4166,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130800712</v>
+        <v>130800669</v>
       </c>
       <c r="B34" t="n">
         <v>79243</v>
@@ -4201,10 +4201,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>489143</v>
+        <v>489170</v>
       </c>
       <c r="R34" t="n">
-        <v>6720114</v>
+        <v>6720167</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4236,7 +4236,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4246,7 +4246,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4273,7 +4273,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130800669</v>
+        <v>130800712</v>
       </c>
       <c r="B35" t="n">
         <v>79243</v>
@@ -4308,10 +4308,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>489170</v>
+        <v>489143</v>
       </c>
       <c r="R35" t="n">
-        <v>6720167</v>
+        <v>6720114</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4343,7 +4343,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4353,7 +4353,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4380,7 +4380,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130800676</v>
+        <v>130800679</v>
       </c>
       <c r="B36" t="n">
         <v>79243</v>
@@ -4415,10 +4415,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>489151</v>
+        <v>489122</v>
       </c>
       <c r="R36" t="n">
-        <v>6720144</v>
+        <v>6720120</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4450,7 +4450,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4460,7 +4460,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4487,7 +4487,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130800679</v>
+        <v>130800676</v>
       </c>
       <c r="B37" t="n">
         <v>79243</v>
@@ -4522,10 +4522,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>489122</v>
+        <v>489151</v>
       </c>
       <c r="R37" t="n">
-        <v>6720120</v>
+        <v>6720144</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4557,7 +4557,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4567,7 +4567,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4701,32 +4701,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130800608</v>
+        <v>130800714</v>
       </c>
       <c r="B39" t="n">
-        <v>92179</v>
+        <v>79243</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4736,10 +4736,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>489214</v>
+        <v>489163</v>
       </c>
       <c r="R39" t="n">
-        <v>6719996</v>
+        <v>6720122</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4771,7 +4771,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4915,7 +4915,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130800714</v>
+        <v>130800677</v>
       </c>
       <c r="B41" t="n">
         <v>79243</v>
@@ -4950,10 +4950,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>489163</v>
+        <v>489132</v>
       </c>
       <c r="R41" t="n">
-        <v>6720122</v>
+        <v>6720123</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4985,7 +4985,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4995,7 +4995,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5022,32 +5022,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130800677</v>
+        <v>130800608</v>
       </c>
       <c r="B42" t="n">
-        <v>79243</v>
+        <v>92179</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5057,10 +5057,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>489132</v>
+        <v>489214</v>
       </c>
       <c r="R42" t="n">
-        <v>6720123</v>
+        <v>6719996</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5092,7 +5092,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5102,7 +5102,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5129,7 +5129,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130800684</v>
+        <v>130800681</v>
       </c>
       <c r="B43" t="n">
         <v>79243</v>
@@ -5164,10 +5164,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>489177</v>
+        <v>489138</v>
       </c>
       <c r="R43" t="n">
-        <v>6720066</v>
+        <v>6720092</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5199,7 +5199,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5209,7 +5209,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5236,7 +5236,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130800709</v>
+        <v>130800684</v>
       </c>
       <c r="B44" t="n">
         <v>79243</v>
@@ -5271,10 +5271,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>489094</v>
+        <v>489177</v>
       </c>
       <c r="R44" t="n">
-        <v>6720086</v>
+        <v>6720066</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5343,7 +5343,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130800667</v>
+        <v>130800709</v>
       </c>
       <c r="B45" t="n">
         <v>79243</v>
@@ -5378,10 +5378,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>489199</v>
+        <v>489094</v>
       </c>
       <c r="R45" t="n">
-        <v>6720176</v>
+        <v>6720086</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5423,7 +5423,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5450,7 +5450,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130800681</v>
+        <v>130800667</v>
       </c>
       <c r="B46" t="n">
         <v>79243</v>
@@ -5485,10 +5485,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>489138</v>
+        <v>489199</v>
       </c>
       <c r="R46" t="n">
-        <v>6720092</v>
+        <v>6720176</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5520,7 +5520,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5530,7 +5530,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6311,7 +6311,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130800683</v>
+        <v>130800680</v>
       </c>
       <c r="B54" t="n">
         <v>79243</v>
@@ -6346,10 +6346,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>489169</v>
+        <v>489131</v>
       </c>
       <c r="R54" t="n">
-        <v>6720075</v>
+        <v>6720110</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6381,7 +6381,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6391,7 +6391,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6418,50 +6418,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130800637</v>
+        <v>130800683</v>
       </c>
       <c r="B55" t="n">
-        <v>8451</v>
+        <v>79243</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>489091</v>
+        <v>489169</v>
       </c>
       <c r="R55" t="n">
-        <v>6720083</v>
+        <v>6720075</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6493,7 +6488,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6503,7 +6498,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6512,7 +6507,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6531,45 +6525,50 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130800680</v>
+        <v>130800637</v>
       </c>
       <c r="B56" t="n">
-        <v>79243</v>
+        <v>8451</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>489131</v>
+        <v>489091</v>
       </c>
       <c r="R56" t="n">
-        <v>6720110</v>
+        <v>6720083</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6601,7 +6600,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6611,7 +6610,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6620,6 +6619,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6638,7 +6638,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130800702</v>
+        <v>130800691</v>
       </c>
       <c r="B57" t="n">
         <v>79243</v>
@@ -6673,10 +6673,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>489258</v>
+        <v>489214</v>
       </c>
       <c r="R57" t="n">
-        <v>6719949</v>
+        <v>6720016</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6708,7 +6708,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6718,7 +6718,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6745,7 +6745,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130800708</v>
+        <v>130800702</v>
       </c>
       <c r="B58" t="n">
         <v>79243</v>
@@ -6780,10 +6780,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>489077</v>
+        <v>489258</v>
       </c>
       <c r="R58" t="n">
-        <v>6720065</v>
+        <v>6719949</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6815,7 +6815,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6852,50 +6852,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130800768</v>
+        <v>130800708</v>
       </c>
       <c r="B59" t="n">
-        <v>5177</v>
+        <v>79243</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>489234</v>
+        <v>489077</v>
       </c>
       <c r="R59" t="n">
-        <v>6719934</v>
+        <v>6720065</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6927,7 +6922,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6937,7 +6932,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6964,50 +6959,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130800604</v>
+        <v>130800705</v>
       </c>
       <c r="B60" t="n">
-        <v>5197</v>
+        <v>79243</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>489244</v>
+        <v>489144</v>
       </c>
       <c r="R60" t="n">
-        <v>6719935</v>
+        <v>6719996</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7039,7 +7029,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7049,7 +7039,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7188,45 +7178,50 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130800691</v>
+        <v>130800604</v>
       </c>
       <c r="B62" t="n">
-        <v>79243</v>
+        <v>5197</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>105930</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>489214</v>
+        <v>489244</v>
       </c>
       <c r="R62" t="n">
-        <v>6720016</v>
+        <v>6719935</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7258,7 +7253,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7268,7 +7263,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7295,45 +7290,50 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130800705</v>
+        <v>130800768</v>
       </c>
       <c r="B63" t="n">
-        <v>79243</v>
+        <v>5177</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>489144</v>
+        <v>489234</v>
       </c>
       <c r="R63" t="n">
-        <v>6719996</v>
+        <v>6719934</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7365,7 +7365,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7375,7 +7375,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7402,7 +7402,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130800692</v>
+        <v>130800674</v>
       </c>
       <c r="B64" t="n">
         <v>79243</v>
@@ -7437,10 +7437,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>489211</v>
+        <v>489168</v>
       </c>
       <c r="R64" t="n">
-        <v>6720011</v>
+        <v>6720197</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7472,7 +7472,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7482,7 +7482,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7509,7 +7509,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130800674</v>
+        <v>130800665</v>
       </c>
       <c r="B65" t="n">
         <v>79243</v>
@@ -7544,10 +7544,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>489168</v>
+        <v>489208</v>
       </c>
       <c r="R65" t="n">
-        <v>6720197</v>
+        <v>6720188</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7579,7 +7579,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7589,7 +7589,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7616,7 +7616,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130800665</v>
+        <v>130800694</v>
       </c>
       <c r="B66" t="n">
         <v>79243</v>
@@ -7651,10 +7651,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>489208</v>
+        <v>489214</v>
       </c>
       <c r="R66" t="n">
-        <v>6720188</v>
+        <v>6719991</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7686,7 +7686,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7696,7 +7696,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7723,7 +7723,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130800694</v>
+        <v>130800692</v>
       </c>
       <c r="B67" t="n">
         <v>79243</v>
@@ -7758,10 +7758,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>489214</v>
+        <v>489211</v>
       </c>
       <c r="R67" t="n">
-        <v>6719991</v>
+        <v>6720011</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7793,7 +7793,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7803,7 +7803,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD67" t="b">

--- a/artfynd/A 62861-2025 artfynd.xlsx
+++ b/artfynd/A 62861-2025 artfynd.xlsx
@@ -1464,10 +1464,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130800706</v>
+        <v>130800627</v>
       </c>
       <c r="B9" t="n">
-        <v>79243</v>
+        <v>57881</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1475,34 +1475,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>489143</v>
+        <v>489163</v>
       </c>
       <c r="R9" t="n">
-        <v>6720009</v>
+        <v>6719987</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1534,7 +1539,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1549,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,10 +1576,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130800693</v>
+        <v>130800622</v>
       </c>
       <c r="B10" t="n">
-        <v>79243</v>
+        <v>57881</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1582,34 +1587,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>489211</v>
+        <v>489171</v>
       </c>
       <c r="R10" t="n">
-        <v>6720001</v>
+        <v>6720048</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1641,7 +1651,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1651,7 +1661,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1678,7 +1688,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130800672</v>
+        <v>130800706</v>
       </c>
       <c r="B11" t="n">
         <v>79243</v>
@@ -1713,10 +1723,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>489170</v>
+        <v>489143</v>
       </c>
       <c r="R11" t="n">
-        <v>6720188</v>
+        <v>6720009</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1748,7 +1758,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1758,7 +1768,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1785,7 +1795,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130800721</v>
+        <v>130800693</v>
       </c>
       <c r="B12" t="n">
         <v>79243</v>
@@ -1820,10 +1830,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>489189</v>
+        <v>489211</v>
       </c>
       <c r="R12" t="n">
-        <v>6720073</v>
+        <v>6720001</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1855,7 +1865,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1865,7 +1875,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1892,10 +1902,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130800627</v>
+        <v>130800672</v>
       </c>
       <c r="B13" t="n">
-        <v>57881</v>
+        <v>79243</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1903,39 +1913,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>489163</v>
+        <v>489170</v>
       </c>
       <c r="R13" t="n">
-        <v>6719987</v>
+        <v>6720188</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1967,7 +1972,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1977,7 +1982,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2004,10 +2009,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130800622</v>
+        <v>130800721</v>
       </c>
       <c r="B14" t="n">
-        <v>57881</v>
+        <v>79243</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2015,39 +2020,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>489171</v>
+        <v>489189</v>
       </c>
       <c r="R14" t="n">
-        <v>6720048</v>
+        <v>6720073</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2079,7 +2079,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2116,45 +2116,50 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130800671</v>
+        <v>130800641</v>
       </c>
       <c r="B15" t="n">
-        <v>79243</v>
+        <v>8451</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>489159</v>
+        <v>489210</v>
       </c>
       <c r="R15" t="n">
-        <v>6720170</v>
+        <v>6720036</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2186,7 +2191,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2196,7 +2201,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2205,6 +2210,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2223,45 +2229,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130800689</v>
+        <v>130800634</v>
       </c>
       <c r="B16" t="n">
-        <v>79243</v>
+        <v>8451</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>489171</v>
+        <v>489196</v>
       </c>
       <c r="R16" t="n">
-        <v>6720037</v>
+        <v>6720103</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2293,7 +2304,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2303,7 +2314,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2312,6 +2323,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2330,50 +2342,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130800641</v>
+        <v>130800671</v>
       </c>
       <c r="B17" t="n">
-        <v>8451</v>
+        <v>79243</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>489210</v>
+        <v>489159</v>
       </c>
       <c r="R17" t="n">
-        <v>6720036</v>
+        <v>6720170</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2405,7 +2412,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2415,7 +2422,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2424,7 +2431,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2443,50 +2449,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130800634</v>
+        <v>130800609</v>
       </c>
       <c r="B18" t="n">
-        <v>8451</v>
+        <v>91808</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>489196</v>
+        <v>489172</v>
       </c>
       <c r="R18" t="n">
-        <v>6720103</v>
+        <v>6720186</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2518,7 +2519,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2528,7 +2529,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2537,7 +2538,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2556,10 +2556,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130800609</v>
+        <v>130800689</v>
       </c>
       <c r="B19" t="n">
-        <v>91808</v>
+        <v>79243</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2567,21 +2567,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>489172</v>
+        <v>489171</v>
       </c>
       <c r="R19" t="n">
-        <v>6720186</v>
+        <v>6720037</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2626,7 +2626,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2636,7 +2636,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2663,10 +2663,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130800621</v>
+        <v>130800710</v>
       </c>
       <c r="B20" t="n">
-        <v>57881</v>
+        <v>79243</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2674,39 +2674,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>489175</v>
+        <v>489124</v>
       </c>
       <c r="R20" t="n">
-        <v>6720065</v>
+        <v>6720109</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2738,7 +2733,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2748,7 +2743,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2775,7 +2770,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130800710</v>
+        <v>130800668</v>
       </c>
       <c r="B21" t="n">
         <v>79243</v>
@@ -2810,10 +2805,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>489124</v>
+        <v>489197</v>
       </c>
       <c r="R21" t="n">
-        <v>6720109</v>
+        <v>6720167</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2845,7 +2840,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2855,7 +2850,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2882,10 +2877,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130800668</v>
+        <v>130800621</v>
       </c>
       <c r="B22" t="n">
-        <v>79243</v>
+        <v>57881</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2893,34 +2888,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>489197</v>
+        <v>489175</v>
       </c>
       <c r="R22" t="n">
-        <v>6720167</v>
+        <v>6720065</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2952,7 +2952,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3310,32 +3310,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130800695</v>
+        <v>130800606</v>
       </c>
       <c r="B26" t="n">
-        <v>79243</v>
+        <v>92179</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3345,10 +3345,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>489231</v>
+        <v>489169</v>
       </c>
       <c r="R26" t="n">
-        <v>6719941</v>
+        <v>6720185</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3380,7 +3380,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3390,7 +3390,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3417,7 +3417,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130800687</v>
+        <v>130800695</v>
       </c>
       <c r="B27" t="n">
         <v>79243</v>
@@ -3452,10 +3452,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>489175</v>
+        <v>489231</v>
       </c>
       <c r="R27" t="n">
-        <v>6720053</v>
+        <v>6719941</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3487,7 +3487,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3524,7 +3524,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130800725</v>
+        <v>130800687</v>
       </c>
       <c r="B28" t="n">
         <v>79243</v>
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>489332</v>
+        <v>489175</v>
       </c>
       <c r="R28" t="n">
-        <v>6720052</v>
+        <v>6720053</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3594,7 +3594,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3604,7 +3604,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3631,7 +3631,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130800696</v>
+        <v>130800725</v>
       </c>
       <c r="B29" t="n">
         <v>79243</v>
@@ -3666,10 +3666,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>489243</v>
+        <v>489332</v>
       </c>
       <c r="R29" t="n">
-        <v>6719933</v>
+        <v>6720052</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3701,7 +3701,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3738,32 +3738,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130800606</v>
+        <v>130800696</v>
       </c>
       <c r="B30" t="n">
-        <v>92179</v>
+        <v>79243</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3773,10 +3773,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>489169</v>
+        <v>489243</v>
       </c>
       <c r="R30" t="n">
-        <v>6720185</v>
+        <v>6719933</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3808,7 +3808,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3818,7 +3818,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4701,32 +4701,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130800714</v>
+        <v>130800608</v>
       </c>
       <c r="B39" t="n">
-        <v>79243</v>
+        <v>92179</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4736,10 +4736,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>489163</v>
+        <v>489214</v>
       </c>
       <c r="R39" t="n">
-        <v>6720122</v>
+        <v>6719996</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4771,7 +4771,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4808,7 +4808,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130800707</v>
+        <v>130800714</v>
       </c>
       <c r="B40" t="n">
         <v>79243</v>
@@ -4843,10 +4843,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>489119</v>
+        <v>489163</v>
       </c>
       <c r="R40" t="n">
-        <v>6720040</v>
+        <v>6720122</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4878,7 +4878,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4915,7 +4915,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130800677</v>
+        <v>130800707</v>
       </c>
       <c r="B41" t="n">
         <v>79243</v>
@@ -4950,10 +4950,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>489132</v>
+        <v>489119</v>
       </c>
       <c r="R41" t="n">
-        <v>6720123</v>
+        <v>6720040</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4985,7 +4985,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4995,7 +4995,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5022,32 +5022,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130800608</v>
+        <v>130800677</v>
       </c>
       <c r="B42" t="n">
-        <v>92179</v>
+        <v>79243</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5057,10 +5057,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>489214</v>
+        <v>489132</v>
       </c>
       <c r="R42" t="n">
-        <v>6719996</v>
+        <v>6720123</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5092,7 +5092,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5102,7 +5102,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5664,10 +5664,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130800610</v>
+        <v>130800704</v>
       </c>
       <c r="B48" t="n">
-        <v>91808</v>
+        <v>79243</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5675,21 +5675,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5699,10 +5699,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>489216</v>
+        <v>489180</v>
       </c>
       <c r="R48" t="n">
-        <v>6719995</v>
+        <v>6719972</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5734,7 +5734,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5744,7 +5744,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5771,7 +5771,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130800704</v>
+        <v>130800715</v>
       </c>
       <c r="B49" t="n">
         <v>79243</v>
@@ -5806,10 +5806,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>489180</v>
+        <v>489166</v>
       </c>
       <c r="R49" t="n">
-        <v>6719972</v>
+        <v>6720127</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5841,7 +5841,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5878,10 +5878,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130800715</v>
+        <v>130800610</v>
       </c>
       <c r="B50" t="n">
-        <v>79243</v>
+        <v>91808</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5889,21 +5889,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5913,10 +5913,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>489166</v>
+        <v>489216</v>
       </c>
       <c r="R50" t="n">
-        <v>6720127</v>
+        <v>6719995</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5948,7 +5948,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5985,10 +5985,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130800673</v>
+        <v>130800630</v>
       </c>
       <c r="B51" t="n">
-        <v>79243</v>
+        <v>57881</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5996,34 +5996,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>489180</v>
+        <v>489207</v>
       </c>
       <c r="R51" t="n">
-        <v>6720180</v>
+        <v>6720041</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6055,7 +6060,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6065,7 +6070,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6092,10 +6097,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130800630</v>
+        <v>130800673</v>
       </c>
       <c r="B52" t="n">
-        <v>57881</v>
+        <v>79243</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6103,39 +6108,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>489207</v>
+        <v>489180</v>
       </c>
       <c r="R52" t="n">
-        <v>6720041</v>
+        <v>6720180</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6167,7 +6167,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6177,7 +6177,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7178,10 +7178,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130800604</v>
+        <v>130800768</v>
       </c>
       <c r="B62" t="n">
-        <v>5197</v>
+        <v>5177</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7189,27 +7189,27 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -7218,10 +7218,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>489244</v>
+        <v>489234</v>
       </c>
       <c r="R62" t="n">
-        <v>6719935</v>
+        <v>6719934</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7253,7 +7253,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7263,7 +7263,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7290,10 +7290,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130800768</v>
+        <v>130800604</v>
       </c>
       <c r="B63" t="n">
-        <v>5177</v>
+        <v>5197</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7301,27 +7301,27 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -7330,10 +7330,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>489234</v>
+        <v>489244</v>
       </c>
       <c r="R63" t="n">
-        <v>6719934</v>
+        <v>6719935</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7365,7 +7365,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7375,7 +7375,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7830,10 +7830,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130800711</v>
+        <v>130800620</v>
       </c>
       <c r="B68" t="n">
-        <v>79243</v>
+        <v>57881</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7841,34 +7841,39 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>489138</v>
+        <v>489144</v>
       </c>
       <c r="R68" t="n">
-        <v>6720109</v>
+        <v>6720087</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7900,7 +7905,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7910,7 +7915,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7937,10 +7942,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130800620</v>
+        <v>130800711</v>
       </c>
       <c r="B69" t="n">
-        <v>57881</v>
+        <v>79243</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7948,39 +7953,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>489144</v>
+        <v>489138</v>
       </c>
       <c r="R69" t="n">
-        <v>6720087</v>
+        <v>6720109</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8012,7 +8012,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8022,7 +8022,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD69" t="b">
